--- a/output/full_scan/batch_seq7_2026-08-10.xlsx
+++ b/output/full_scan/batch_seq7_2026-08-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O80"/>
+  <dimension ref="A1:O76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>759.8912550996769</v>
+        <v>719.8912550996769</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1195</v>
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>657.5891083167379</v>
+        <v>697.5891083167379</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>83.5</v>
@@ -644,7 +644,7 @@
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>643.1425714737663</v>
+        <v>683.1425714737663</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>2845</v>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>639.0725445667794</v>
+        <v>679.0725445667794</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>145.5</v>
@@ -739,21 +739,21 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6530</v>
+        <v>6642</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>592.5901958258647</v>
+        <v>628.6846060253871</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>82.5</v>
+        <v>83.3</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>55.3255704569258</v>
+        <v>60.2889815494212</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>23.70751846741007</v>
+        <v>17.20897975546421</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.819285779096404</v>
+        <v>4.284213476239731</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>1</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>2.232003913636197</v>
+        <v>1.156990142525024</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6642</v>
+        <v>6530</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>588.6846060253871</v>
+        <v>612.5901958258647</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>83.3</v>
+        <v>82.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>60.2889815494212</v>
+        <v>55.3255704569258</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>17.20897975546421</v>
+        <v>23.70751846741007</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>4.284213476239731</v>
+        <v>1.819285779096404</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>1</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.156990142525024</v>
+        <v>2.232003913636197</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6789</v>
+        <v>6570</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>580.558020671125</v>
+        <v>584.5426196577403</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>441.5</v>
+        <v>57.3</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>45.60821881364068</v>
+        <v>62.78642047667233</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>22.20721067968122</v>
+        <v>17.51839189660703</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.8306212272732345</v>
+        <v>2.821798166333596</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.7751631651231854</v>
+        <v>1.020147977210087</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6716</v>
+        <v>6651</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>568.8507934837611</v>
+        <v>569.8512544222294</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>66.65619037802345</v>
+        <v>55.2073267495169</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>21.99245011801612</v>
+        <v>21.67273944619703</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.408137471200302</v>
+        <v>2.739427404341888</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>2.825541977084809</v>
+        <v>2.065680453017155</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6672</v>
+        <v>6789</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>559.6551418881993</v>
+        <v>540.558020671125</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>251.5</v>
+        <v>441.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>56.67183179011068</v>
+        <v>45.60821881364068</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>22.66951128365132</v>
+        <v>22.20721067968122</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.069419210418419</v>
+        <v>0.8306212272732345</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,48 +994,48 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>3.476117446306505</v>
+        <v>0.7751631651231854</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6669</v>
+        <v>6806</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>551.6128318963862</v>
+        <v>528.7768356926886</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>6010</v>
+        <v>3.51</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G11" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>60.0720042164613</v>
+        <v>31.69502831466412</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>19.81404541536655</v>
+        <v>32.5931975692691</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.8392590884643881</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>78.62252026483554</v>
+        <v>0.4112821443334762</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6570</v>
+        <v>6672</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>544.5426196577403</v>
+        <v>519.6551418881993</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>57.3</v>
+        <v>251.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>62.78642047667233</v>
+        <v>56.67183179011068</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>17.51839189660703</v>
+        <v>22.66951128365132</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2.821798166333596</v>
+        <v>2.069419210418419</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>1.020147977210087</v>
+        <v>3.476117446306505</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6651</v>
+        <v>6669</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>529.8512544222294</v>
+        <v>511.6128318963861</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>135</v>
+        <v>6010</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>55.2073267495169</v>
+        <v>60.0720042164613</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>21.67273944619703</v>
+        <v>19.81404541536655</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.739427404341888</v>
+        <v>0.8392590884643881</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,48 +1153,48 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>2.065680453017155</v>
+        <v>78.62252026483554</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6806</v>
+        <v>6640</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>528.7768356926886</v>
+        <v>485.7200540579751</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>3.51</v>
+        <v>1005</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G14" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>31.69502831466412</v>
+        <v>54.59927404791888</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>32.5931975692691</v>
+        <v>20.21834003709472</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>0.2956184699271068</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.4112821443334762</v>
+        <v>20.53216758736876</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6805</v>
+        <v>6584</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>507.7563613200152</v>
+        <v>469.236949088452</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1755</v>
+        <v>522</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>61.11310339296048</v>
+        <v>46.18266784822475</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>30.83188965682062</v>
+        <v>30.31428625478637</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.860807352615913</v>
+        <v>3.581754449205871</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>58.4128392384233</v>
+        <v>7.870487465498378</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6830</v>
+        <v>6742</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>493.4382362107434</v>
+        <v>468.4734612140247</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>424.5</v>
+        <v>44.1</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>52.54861417169353</v>
+        <v>40.82155755577556</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>21.29932834693594</v>
+        <v>21.68416843291506</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.119607925823429</v>
+        <v>0.3084014009874118</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>15.16503674177781</v>
+        <v>0.5583314277996085</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6533</v>
+        <v>6805</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>487.4846734611374</v>
+        <v>467.7563613200151</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>250</v>
+        <v>1755</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>63.32615909617144</v>
+        <v>61.11310339296048</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>17.84670684157508</v>
+        <v>30.83188965682062</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>3.13588276451926</v>
+        <v>1.860807352615913</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>3.770773791979233</v>
+        <v>58.4128392384233</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6743</v>
+        <v>6715</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>477.5575186325199</v>
+        <v>463.4202825676861</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>25.95</v>
+        <v>363.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>33.87861410110625</v>
+        <v>47.29255753055375</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>30.65643176615675</v>
+        <v>11.21529419691228</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.8234789719637171</v>
+        <v>0.4688925881836271</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.5587045831037137</v>
+        <v>1.714932397652252</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6834</v>
+        <v>6830</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>天二科技</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>473.5071841860943</v>
+        <v>453.4382362107434</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>96.59999999999999</v>
+        <v>424.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>51.42995958715492</v>
+        <v>52.54861417169353</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>18.11742300721276</v>
+        <v>21.29932834693594</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.088022397359117</v>
+        <v>1.119607925823429</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.2480144407518252</v>
+        <v>15.16503674177781</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6640</v>
+        <v>6533</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>465.7200540579751</v>
+        <v>447.4846734611374</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1005</v>
+        <v>250</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>54.59927404791888</v>
+        <v>63.32615909617144</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>20.21834003709472</v>
+        <v>17.84670684157508</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.2956184699271068</v>
+        <v>3.13588276451926</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>20.53216758736876</v>
+        <v>3.770773791979233</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6715</v>
+        <v>6743</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>463.4202825676861</v>
+        <v>437.5575186325199</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>363.5</v>
+        <v>25.95</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>47.29255753055375</v>
+        <v>33.87861410110625</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>11.21529419691228</v>
+        <v>30.65643176615675</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.4688925881836271</v>
+        <v>0.8234789719637171</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>1.714932397652252</v>
+        <v>-0.5587045831037137</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6756</v>
+        <v>6561</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>447.6224378131971</v>
+        <v>433.7076490833803</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>99.90000000000001</v>
+        <v>327.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>54.80601789098797</v>
+        <v>49.0884234657758</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>18.41246145425619</v>
+        <v>16.62347082415516</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.6046125239328692</v>
+        <v>0.5880489855703774</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>1.074441310961462</v>
+        <v>1.208785345212072</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6689</v>
+        <v>6834</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>443.2327605734614</v>
+        <v>433.5071841860943</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>64.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>58.1748589731627</v>
+        <v>51.42995958715492</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>24.78905494688414</v>
+        <v>18.11742300721276</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.359868348421285</v>
+        <v>1.088022397359117</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.6793548770186604</v>
+        <v>0.2480144407518252</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6742</v>
+        <v>6680</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>438.4734612140247</v>
+        <v>432.1101223172679</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>44.1</v>
+        <v>52.9</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>40.82155755577556</v>
+        <v>51.35654851602799</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>21.68416843291506</v>
+        <v>8.928063920683451</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.3084014009874118</v>
+        <v>0.8490717286048675</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.5583314277996085</v>
+        <v>-1.648866142513686</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6684</v>
+        <v>6689</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>436.0049317990572</v>
+        <v>423.2327605734614</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>50.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>51.55659956406806</v>
+        <v>58.1748589731627</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>16.81503294795015</v>
+        <v>24.78905494688414</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.238054269529925</v>
+        <v>1.359868348421285</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.1866763663144728</v>
+        <v>0.6793548770186604</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, foreign_buy_3d, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6584</v>
+        <v>6756</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>429.236949088452</v>
+        <v>407.6224378131971</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>522</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>46.18266784822475</v>
+        <v>54.80601789098797</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>30.31428625478637</v>
+        <v>18.41246145425619</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>3.581754449205871</v>
+        <v>0.6046125239328692</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>7.870487465498378</v>
+        <v>1.074441310961462</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6658</v>
+        <v>6517</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>422.8295496624563</v>
+        <v>402.9592611202101</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>161.5</v>
+        <v>62</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>49.57803870758161</v>
+        <v>43.65105831595943</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>23.76831546778813</v>
+        <v>17.74264075525872</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.7615987252108752</v>
+        <v>0.1284796058816047</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>2.208044636336305</v>
+        <v>-0.4950825195650075</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6691</v>
+        <v>6494</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>421.3977196089454</v>
+        <v>402.5202926201114</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>732</v>
+        <v>55.2</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>56.39326079237441</v>
+        <v>54.1229302849265</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>16.12405063835193</v>
+        <v>27.54430289878499</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.7817796276097244</v>
+        <v>1.14580192141777</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>6.3943927806036</v>
+        <v>0.9095012201500574</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6680</v>
+        <v>6658</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>412.1101223172679</v>
+        <v>382.8295496624563</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>52.9</v>
+        <v>161.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>51.35654851602799</v>
+        <v>49.57803870758161</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>8.928063920683451</v>
+        <v>23.76831546778813</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.8490717286048675</v>
+        <v>0.7615987252108752</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-1.648866142513686</v>
+        <v>2.208044636336305</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6693</v>
+        <v>6691</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>409.4159036416215</v>
+        <v>381.3977196089454</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>184</v>
+        <v>732</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>50.38863430194367</v>
+        <v>56.39326079237441</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>26.94908635017923</v>
+        <v>16.12405063835193</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>3.328927515200341</v>
+        <v>0.7817796276097244</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>1.716256404857681</v>
+        <v>6.3943927806036</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6561</v>
+        <v>6679</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>393.7076490833803</v>
+        <v>369.2154689917006</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>327.5</v>
+        <v>215.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>49.0884234657758</v>
+        <v>43.50356665864479</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>16.62347082415516</v>
+        <v>31.37443742697766</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.5880489855703774</v>
+        <v>0.7293921328468287</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>1.208785345212072</v>
+        <v>2.322547877028937</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6517</v>
+        <v>6591</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>382.9592611202101</v>
+        <v>357.2464052793781</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>62</v>
+        <v>44.9</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>43.65105831595943</v>
+        <v>42.13820941058614</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>17.74264075525872</v>
+        <v>45.03423550294112</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.1284796058816047</v>
+        <v>1.143389778792955</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.4950825195650075</v>
+        <v>0.4851264654756431</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6831</v>
+        <v>6664</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>367.7859982476213</v>
+        <v>348.442314200225</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>619</v>
+        <v>348</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>47.22838285476606</v>
+        <v>47.45542651341767</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>23.85039667755416</v>
+        <v>25.70798519345708</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.92311151391005</v>
+        <v>0.7454550082529414</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>9.930812126126725</v>
+        <v>1.261714691823794</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6494</v>
+        <v>6556</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>362.5202926201114</v>
+        <v>341</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>55.2</v>
+        <v>61.7</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>54.1229302849265</v>
+        <v>34.5926465168049</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>27.54430289878499</v>
+        <v>24.57604318797957</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.14580192141777</v>
+        <v>8.973581920851069</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.9095012201500574</v>
+        <v>0.1846656717517687</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6770</v>
+        <v>6548</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>354.947886614597</v>
+        <v>336.6128649838843</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>67.59999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>53.55467541253191</v>
+        <v>53.05372729290665</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>16.20563895511379</v>
+        <v>19.98922929557009</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.169070819550472</v>
+        <v>0.6025674412759904</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>1.266537678945586</v>
+        <v>1.19829039312493</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>354.0242334417147</v>
+        <v>334.0242334417147</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>88</v>
@@ -2382,21 +2382,21 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6526</v>
+        <v>6588</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>353.9320709299399</v>
+        <v>329.377052895135</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>627</v>
+        <v>90.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>54.46587496093099</v>
+        <v>52.17663244556365</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>18.71173356855546</v>
+        <v>19.66415085566471</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.5119133710669493</v>
+        <v>0.4659584938125662</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>12.25517051224604</v>
+        <v>1.975970167190084</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6679</v>
+        <v>6831</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>349.2154689917006</v>
+        <v>327.7859982476213</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>215.5</v>
+        <v>619</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>43.50356665864479</v>
+        <v>47.22838285476606</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>31.37443742697766</v>
+        <v>23.85039667755416</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.7293921328468287</v>
+        <v>0.92311151391005</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>2.322547877028937</v>
+        <v>9.930812126126725</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6708</v>
+        <v>6719</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>347.7426857563657</v>
+        <v>325.9158525771313</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>38.8</v>
+        <v>205.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>51.82418142691544</v>
+        <v>40.82978142623313</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>13.21736218561355</v>
+        <v>20.79154253108725</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.3136627576445495</v>
+        <v>1.026644398199289</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.6951912532277955</v>
+        <v>-0.1702043061906515</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, obv_uptrend, williams_r_recovery, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6641</v>
+        <v>6577</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>344.6382874993881</v>
+        <v>323.5857798095538</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>18.2</v>
+        <v>80.3</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>56.43482678571636</v>
+        <v>51.31890801893034</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>12.00180458616351</v>
+        <v>23.16408226615743</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.1768953973291743</v>
+        <v>0.1266768507117398</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.083393593295577</v>
+        <v>-0.3933678215734115</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6525</v>
+        <v>6770</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>342.9680112976309</v>
+        <v>314.947886614597</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>142</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>48.54244158966806</v>
+        <v>53.55467541253191</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>22.13916893059711</v>
+        <v>16.20563895511379</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.5780713410641339</v>
+        <v>1.169070819550472</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.6126071199251202</v>
+        <v>1.266537678945586</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6579</v>
+        <v>6526</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>337.1238093422038</v>
+        <v>313.9320709299399</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>164.5</v>
+        <v>627</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>49.98277258133356</v>
+        <v>54.46587496093099</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>14.21627861852767</v>
+        <v>18.71173356855546</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.464210850067146</v>
+        <v>0.5119133710669493</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,11 +2690,11 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.4912583213197818</v>
+        <v>12.25517051224604</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2711,7 @@
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>336.7794053218618</v>
+        <v>306.7794053218618</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>20.15</v>
@@ -2753,21 +2753,21 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6591</v>
+        <v>6641</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>327.2464052793781</v>
+        <v>304.6382874993881</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>44.9</v>
+        <v>18.2</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>42.13820941058614</v>
+        <v>56.43482678571636</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45.03423550294112</v>
+        <v>12.00180458616351</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.143389778792955</v>
+        <v>0.1768953973291743</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.4851264654756431</v>
+        <v>0.083393593295577</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6719</v>
+        <v>6525</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>325.9158525771313</v>
+        <v>302.9680112976309</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>205.5</v>
+        <v>142</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>40.82978142623313</v>
+        <v>48.54244158966806</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>20.79154253108725</v>
+        <v>22.13916893059711</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.026644398199289</v>
+        <v>0.5780713410641339</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.1702043061906515</v>
+        <v>-0.6126071199251202</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6556</v>
+        <v>6579</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>321</v>
+        <v>297.1238093422038</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>61.7</v>
+        <v>164.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>34.5926465168049</v>
+        <v>49.98277258133356</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>24.57604318797957</v>
+        <v>14.21627861852767</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>8.973581920851069</v>
+        <v>1.464210850067146</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,11 +2902,11 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.1846656717517687</v>
+        <v>0.4912583213197818</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2923,7 @@
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>311.7637366865634</v>
+        <v>291.7637366865634</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>31</v>
@@ -2965,21 +2965,21 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6664</v>
+        <v>6722</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>308.442314200225</v>
+        <v>290.4601890576815</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>348</v>
+        <v>33.25</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>47.45542651341767</v>
+        <v>41.43794222196013</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>25.70798519345708</v>
+        <v>45.09035858844592</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.7454550082529414</v>
+        <v>0.6582239260824728</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>1.261714691823794</v>
+        <v>0.0453051647860042</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6577</v>
+        <v>6683</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>303.5857798095538</v>
+        <v>286.538427429983</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>80.3</v>
+        <v>1230</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>51.31890801893034</v>
+        <v>48.2745948886829</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>23.16408226615743</v>
+        <v>28.25725879420688</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.1266768507117398</v>
+        <v>0.4899732956481283</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.3933678215734115</v>
+        <v>31.4348537002561</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6548</v>
+        <v>6531</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>296.6128649838843</v>
+        <v>284.7992152405097</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>75.7</v>
+        <v>923</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>53.05372729290665</v>
+        <v>55.53775567986045</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>19.98922929557009</v>
+        <v>17.9383876361415</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.6025674412759904</v>
+        <v>1.776806020075897</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>1.19829039312493</v>
+        <v>26.79131172666612</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6588</v>
+        <v>6613</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>289.377052895135</v>
+        <v>278.7082956743713</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>90.5</v>
+        <v>267</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>52.17663244556365</v>
+        <v>39.02089114142221</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>19.66415085566471</v>
+        <v>17.92466641318843</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.4659584938125662</v>
+        <v>1.295821904755391</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>1.975970167190084</v>
+        <v>-2.564751388353312</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6581</v>
+        <v>6546</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>288.2253586697184</v>
+        <v>276.6720293204235</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>108</v>
+        <v>61.1</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>49.67379398493452</v>
+        <v>48.6918563128969</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>13.01856406597112</v>
+        <v>34.25128176075999</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.3520176135133184</v>
+        <v>0.4540382745166306</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.0219361556607685</v>
+        <v>0.8710308901620962</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6515</v>
+        <v>6568</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>281.0314674116885</v>
+        <v>253.4327049767064</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>6830</v>
+        <v>139.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>48.71305714719616</v>
+        <v>44.11459787240925</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>19.23198677474299</v>
+        <v>50.3952196306465</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.9790195446006202</v>
+        <v>0.5120552148809838</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>181.6138323572908</v>
+        <v>2.265521062470729</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6546</v>
+        <v>6667</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>276.6720293204235</v>
+        <v>252.4384138177306</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>61.1</v>
+        <v>235.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>48.6918563128969</v>
+        <v>45.71064707908463</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>34.25128176075999</v>
+        <v>26.92820647933205</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.4540382745166306</v>
+        <v>0.8239079445400816</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.8710308901620962</v>
+        <v>1.098253347595543</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6692</v>
+        <v>6581</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>274.8501039559089</v>
+        <v>248.2253586697184</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>24.25</v>
+        <v>108</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>52.26106510648049</v>
+        <v>49.67379398493452</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>11.43825607522764</v>
+        <v>13.01856406597112</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>3.244331776378185</v>
+        <v>0.3520176135133184</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.5307021697131324</v>
+        <v>0.0219361556607685</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6722</v>
+        <v>6515</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>260.4601890576815</v>
+        <v>241.0314674116884</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>33.25</v>
+        <v>6830</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>41.43794222196013</v>
+        <v>48.71305714719616</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45.09035858844592</v>
+        <v>19.23198677474299</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.6582239260824728</v>
+        <v>0.9790195446006202</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.0453051647860042</v>
+        <v>181.6138323572908</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6667</v>
+        <v>6698</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>252.4384138177306</v>
+        <v>235.1009942776442</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>235.5</v>
+        <v>34.05</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>45.71064707908463</v>
+        <v>44.76379528547555</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>26.92820647933205</v>
+        <v>23.3107845556375</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.8239079445400816</v>
+        <v>0.5893334830166511</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>1.098253347595543</v>
+        <v>0.2970275502286945</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6683</v>
+        <v>6488</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>246.538427429983</v>
+        <v>226.296324417609</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>1230</v>
+        <v>854</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,49 +3520,49 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>48.2745948886829</v>
+        <v>40.00740011950307</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>28.25725879420688</v>
+        <v>19.6361494784886</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.4899732956481283</v>
+        <v>0.6090360424699359</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>31.4348537002561</v>
+        <v>-27.16885309080623</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6597</v>
+        <v>6654</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>245.8405061488688</v>
+        <v>224.6346304023602</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>67.8</v>
+        <v>175.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>52.56550927441516</v>
+        <v>52.30623216854402</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>9.227910220942441</v>
+        <v>20.35072611833792</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>2.222963075213416</v>
+        <v>0.5443752742378344</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>1.657113472402883</v>
+        <v>0.8049146976001036</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6776</v>
+        <v>6695</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>239.3388245766569</v>
+        <v>223.9700088630154</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>54</v>
+        <v>49.05</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>47.18497562275842</v>
+        <v>42.38783163284979</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>21.12908600125668</v>
+        <v>16.84054063700665</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.6309677549372419</v>
+        <v>0.5859369776776999</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.1513933882284058</v>
+        <v>-0.04727762318667</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6613</v>
+        <v>6597</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>238.7082956743713</v>
+        <v>215.8405061488688</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>267</v>
+        <v>67.8</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>39.02089114142221</v>
+        <v>52.56550927441516</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>17.92466641318843</v>
+        <v>9.227910220942441</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.295821904755391</v>
+        <v>2.222963075213416</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-2.564751388353312</v>
+        <v>1.657113472402883</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6488</v>
+        <v>6674</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>226.296324417609</v>
+        <v>211.4543449681333</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>854</v>
+        <v>15.15</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,49 +3732,49 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>40.00740011950307</v>
+        <v>33.09777697734876</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>19.6361494784886</v>
+        <v>27.94371380273006</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.6090360424699359</v>
+        <v>1.233427896138704</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-27.16885309080623</v>
+        <v>-0.0109324870091924</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6568</v>
+        <v>6485</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>213.4327049767064</v>
+        <v>210.1515967327581</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>139.5</v>
+        <v>65.2</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>44.11459787240925</v>
+        <v>46.58153637139367</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>50.3952196306465</v>
+        <v>31.92566440614958</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.5120552148809838</v>
+        <v>0.8886209377032902</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>1</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>2.265521062470729</v>
+        <v>1.451334781405931</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6624</v>
+        <v>6560</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>212.9192891707028</v>
+        <v>208.2895459900261</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>43.55</v>
+        <v>32.75</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>54.1956178298716</v>
+        <v>42.6656646377571</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>10.31840855293046</v>
+        <v>23.55610304861302</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.0808055944507439</v>
+        <v>0.09574777521272169</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>3.456389985290163</v>
+        <v>0.2164267139628419</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6485</v>
+        <v>6486</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>210.1515967327581</v>
+        <v>205.11694768226</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>65.2</v>
+        <v>74.8</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>46.58153637139367</v>
+        <v>37.32295600264841</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>31.92566440614958</v>
+        <v>20.93066759831938</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.8886209377032902</v>
+        <v>0.4384345853634585</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>1.451334781405931</v>
+        <v>-0.0291627746541869</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6668</v>
+        <v>6776</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>206.9074690674686</v>
+        <v>199.3388245766569</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>35.25</v>
+        <v>54</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>47.20786546979786</v>
+        <v>47.18497562275842</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>14.09140970435063</v>
+        <v>21.12908600125668</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.3209328948822644</v>
+        <v>0.6309677549372419</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.1986078361931164</v>
+        <v>0.1513933882284058</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6698</v>
+        <v>6706</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>205.1009942776442</v>
+        <v>195.4078662588853</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>34.05</v>
+        <v>115</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>44.76379528547555</v>
+        <v>47.36422328239001</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>23.3107845556375</v>
+        <v>27.9360274930259</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.5893334830166511</v>
+        <v>1.400283400510497</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.2970275502286945</v>
+        <v>3.154285057340575</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6792</v>
+        <v>6668</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>201.4577717824017</v>
+        <v>186.9074690674686</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>58.1</v>
+        <v>35.25</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>53.53094301456269</v>
+        <v>47.20786546979786</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>20.83237706136118</v>
+        <v>14.09140970435063</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.1071657777679421</v>
+        <v>0.3209328948822644</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.9151082857450872</v>
+        <v>0.1986078361931164</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, cci_momentum</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6695</v>
+        <v>6624</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>193.9700088630154</v>
+        <v>182.9192891707028</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>49.05</v>
+        <v>43.55</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>42.38783163284979</v>
+        <v>54.1956178298716</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>16.84054063700665</v>
+        <v>10.31840855293046</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.5859369776776999</v>
+        <v>0.0808055944507439</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.04727762318667</v>
+        <v>3.456389985290163</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6643</v>
+        <v>6792</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>188.3184728606389</v>
+        <v>181.4577717824017</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>441</v>
+        <v>58.1</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>51.4404446531714</v>
+        <v>53.53094301456269</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>16.8644077092416</v>
+        <v>20.83237706136118</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.6067073503653335</v>
+        <v>0.1071657777679421</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>7.946861437298072</v>
+        <v>0.9151082857450872</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, adx_trending, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6654</v>
+        <v>6552</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>184.6346304023602</v>
+        <v>168.5981297540415</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>175.5</v>
+        <v>24.9</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>52.30623216854402</v>
+        <v>42.38434697611292</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>20.35072611833792</v>
+        <v>22.7585018338222</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.5443752742378344</v>
+        <v>0.259430816537764</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.8049146976001036</v>
+        <v>0.191439221867006</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6573</v>
+        <v>6498</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>183.1716928791651</v>
+        <v>166.1113844479647</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>16.95</v>
+        <v>77</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>42.60033215073253</v>
+        <v>43.16491929246962</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>16.91018142212874</v>
+        <v>38.13070991314</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.5594342595761482</v>
+        <v>0.8679145084146477</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.2575969118523213</v>
+        <v>0.8198042544683419</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6674</v>
+        <v>6573</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>181.4543449681333</v>
+        <v>163.1716928791651</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>15.15</v>
+        <v>16.95</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>33.09777697734876</v>
+        <v>42.60033215073253</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>27.94371380273006</v>
+        <v>16.91018142212874</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.233427896138704</v>
+        <v>0.5594342595761482</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.0109324870091924</v>
+        <v>-0.2575969118523213</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6558</v>
+        <v>6643</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>172.9799379394085</v>
+        <v>158.3184728606389</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>26.75</v>
+        <v>441</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>49.35985312135943</v>
+        <v>51.4404446531714</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>31.78033287105508</v>
+        <v>16.8644077092416</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.9041300013487308</v>
+        <v>0.6067073503653335</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.2548989916106241</v>
+        <v>7.946861437298072</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6560</v>
+        <v>6771</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>168.2895459900261</v>
+        <v>142.8745263239954</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>32.75</v>
+        <v>38</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>42.6656646377571</v>
+        <v>39.90102792412294</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>23.55610304861302</v>
+        <v>13.84143715119434</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.09574777521272169</v>
+        <v>1.307740811853606</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.2164267139628419</v>
+        <v>0.07260361763226519</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6706</v>
+        <v>6558</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>165.4078662588853</v>
+        <v>132.9799379394085</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>115</v>
+        <v>26.75</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>47.36422328239001</v>
+        <v>49.35985312135943</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>27.9360274930259</v>
+        <v>31.78033287105508</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.400283400510497</v>
+        <v>0.9041300013487308</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,223 +4492,11 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>3.154285057340575</v>
+        <v>0.2548989916106241</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="n">
-        <v>6486</v>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>互動</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D77" s="2" t="n">
-        <v>165.11694768226</v>
-      </c>
-      <c r="E77" s="2" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H77" s="2" t="n">
-        <v>37.32295600264841</v>
-      </c>
-      <c r="I77" s="2" t="n">
-        <v>20.93066759831938</v>
-      </c>
-      <c r="J77" s="2" t="n">
-        <v>0.4384345853634585</v>
-      </c>
-      <c r="K77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N77" s="2" t="n">
-        <v>-0.0291627746541869</v>
-      </c>
-      <c r="O77" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="n">
-        <v>6498</v>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>久禾光</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D78" s="2" t="n">
-        <v>146.1113844479647</v>
-      </c>
-      <c r="E78" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H78" s="2" t="n">
-        <v>43.16491929246962</v>
-      </c>
-      <c r="I78" s="2" t="n">
-        <v>38.13070991314</v>
-      </c>
-      <c r="J78" s="2" t="n">
-        <v>0.8679145084146477</v>
-      </c>
-      <c r="K78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N78" s="2" t="n">
-        <v>0.8198042544683419</v>
-      </c>
-      <c r="O78" s="2" t="inlineStr">
-        <is>
           <t>market_above_ma60, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="n">
-        <v>6552</v>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>易華電</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D79" s="2" t="n">
-        <v>138.5981297540415</v>
-      </c>
-      <c r="E79" s="2" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H79" s="2" t="n">
-        <v>42.38434697611292</v>
-      </c>
-      <c r="I79" s="2" t="n">
-        <v>22.7585018338222</v>
-      </c>
-      <c r="J79" s="2" t="n">
-        <v>0.259430816537764</v>
-      </c>
-      <c r="K79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N79" s="2" t="n">
-        <v>0.191439221867006</v>
-      </c>
-      <c r="O79" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="n">
-        <v>6771</v>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>平和環保-創</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D80" s="2" t="n">
-        <v>112.8745263239954</v>
-      </c>
-      <c r="E80" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H80" s="2" t="n">
-        <v>39.90102792412294</v>
-      </c>
-      <c r="I80" s="2" t="n">
-        <v>13.84143715119434</v>
-      </c>
-      <c r="J80" s="2" t="n">
-        <v>1.307740811853606</v>
-      </c>
-      <c r="K80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N80" s="2" t="n">
-        <v>0.07260361763226519</v>
-      </c>
-      <c r="O80" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>

--- a/output/full_scan/batch_seq7_2026-08-10.xlsx
+++ b/output/full_scan/batch_seq7_2026-08-10.xlsx
@@ -428,11 +428,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O76"/>
+  <dimension ref="A1:O113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6781</v>
+        <v>6589</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>719.8912550996769</v>
+        <v>903.1291122950096</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1195</v>
+        <v>50.7</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>63.66996250914878</v>
+        <v>63.20820428277012</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>21.99323176115009</v>
+        <v>20.28430258577195</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>2.089125509967689</v>
+        <v>2.224597440910823</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>32.35333156805501</v>
+        <v>0.4221706655771498</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6532</v>
+        <v>6606</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>697.5891083167379</v>
+        <v>859.2585208683897</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>83.5</v>
+        <v>26.4</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,13 +605,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>61.98118191778797</v>
+        <v>64.9322162182639</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>30.72823203396104</v>
+        <v>11.32805055959344</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.653578451812226</v>
+        <v>1.33234245213</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>1</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>2.656475657580986</v>
+        <v>0.0184664548661789</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6510</v>
+        <v>6716</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>683.1425714737663</v>
+        <v>808.8507934837611</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2845</v>
+        <v>105</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,49 +658,49 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>51.91621449396283</v>
+        <v>66.65619037802345</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>25.15402236835393</v>
+        <v>21.99245011801612</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.54779792100466</v>
+        <v>1.408137471200302</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>58.225230001748</v>
+        <v>2.825541977084809</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6538</v>
+        <v>6491</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>倉和</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>679.0725445667794</v>
+        <v>763.6151179059989</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>145.5</v>
+        <v>379</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>55.34335939424123</v>
+        <v>65.97135344201988</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>22.83368063286276</v>
+        <v>24.23052685244127</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.5449581570377342</v>
+        <v>0.9238484290684073</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.7470759547209362</v>
+        <v>4.415376844735866</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6642</v>
+        <v>6585</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>628.6846060253871</v>
+        <v>759.1229721981631</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>83.3</v>
+        <v>117.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>60.2889815494212</v>
+        <v>47.42447050181128</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>17.20897975546421</v>
+        <v>19.77777410643681</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>4.284213476239731</v>
+        <v>1.738748160150335</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>1</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>1.156990142525024</v>
+        <v>-0.1322649076297377</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6530</v>
+        <v>6811</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>612.5901958258647</v>
+        <v>748.7586716265645</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>82.5</v>
+        <v>235</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>55.3255704569258</v>
+        <v>54.31271275553281</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>23.70751846741007</v>
+        <v>20.28575397640271</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.819285779096404</v>
+        <v>0.5415195298719717</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>2.232003913636197</v>
+        <v>0.4202800286211601</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6570</v>
+        <v>6781</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>584.5426196577403</v>
+        <v>719.8912550996769</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>57.3</v>
+        <v>1195</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>62.78642047667233</v>
+        <v>63.66996250914878</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>17.51839189660703</v>
+        <v>21.99323176115009</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2.821798166333596</v>
+        <v>2.089125509967689</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1.020147977210087</v>
+        <v>32.35333156805501</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6651</v>
+        <v>6598</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>569.8512544222294</v>
+        <v>710.5301595514918</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>135</v>
+        <v>29.4</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>55.2073267495169</v>
+        <v>56.16138578541567</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>21.67273944619703</v>
+        <v>37.81218167631322</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.739427404341888</v>
+        <v>0.3585962222119435</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>2.065680453017155</v>
+        <v>-0.0879665259676758</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6789</v>
+        <v>6532</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>540.558020671125</v>
+        <v>697.5891083167379</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>441.5</v>
+        <v>83.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>45.60821881364068</v>
+        <v>61.98118191778797</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>22.20721067968122</v>
+        <v>30.72823203396104</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.8306212272732345</v>
+        <v>2.653578451812226</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,84 +994,84 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.7751631651231854</v>
+        <v>2.656475657580986</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6806</v>
+        <v>6510</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>528.7768356926886</v>
+        <v>683.1425714737663</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3.51</v>
+        <v>2845</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G11" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>31.69502831466412</v>
+        <v>51.91621449396283</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>32.5931975692691</v>
+        <v>25.15402236835393</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>1.54779792100466</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.4112821443334762</v>
+        <v>58.225230001748</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6672</v>
+        <v>6538</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>519.6551418881993</v>
+        <v>679.0725445667794</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>251.5</v>
+        <v>145.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>56.67183179011068</v>
+        <v>55.34335939424123</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>22.66951128365132</v>
+        <v>22.83368063286276</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2.069419210418419</v>
+        <v>0.5449581570377342</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>3.476117446306505</v>
+        <v>0.7470759547209362</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6669</v>
+        <v>6693</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>511.6128318963861</v>
+        <v>649.4159036416214</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>6010</v>
+        <v>184</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>60.0720042164613</v>
+        <v>50.38863430194367</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>19.81404541536655</v>
+        <v>26.94908635017923</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.8392590884643881</v>
+        <v>3.328927515200341</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>78.62252026483554</v>
+        <v>1.716256404857681</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6640</v>
+        <v>6642</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>485.7200540579751</v>
+        <v>628.6846060253871</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1005</v>
+        <v>83.3</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>54.59927404791888</v>
+        <v>60.2889815494212</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>20.21834003709472</v>
+        <v>17.20897975546421</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.2956184699271068</v>
+        <v>4.284213476239731</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>20.53216758736876</v>
+        <v>1.156990142525024</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6584</v>
+        <v>6761</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>469.236949088452</v>
+        <v>625.7448923331278</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>522</v>
+        <v>168</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>46.18266784822475</v>
+        <v>54.05048169608121</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>30.31428625478637</v>
+        <v>26.02804642597277</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>3.581754449205871</v>
+        <v>2.362822094468798</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>7.870487465498378</v>
+        <v>3.685602557869743</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6742</v>
+        <v>6530</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>468.4734612140247</v>
+        <v>612.5901958258647</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>44.1</v>
+        <v>82.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>40.82155755577556</v>
+        <v>55.3255704569258</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>21.68416843291506</v>
+        <v>23.70751846741007</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.3084014009874118</v>
+        <v>1.819285779096404</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.5583314277996085</v>
+        <v>2.232003913636197</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6805</v>
+        <v>6504</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>467.7563613200151</v>
+        <v>603.0976881410558</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1755</v>
+        <v>39</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>61.11310339296048</v>
+        <v>56.12879605314978</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>30.83188965682062</v>
+        <v>28.8372696995016</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.860807352615913</v>
+        <v>0.3446491781906637</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>58.4128392384233</v>
+        <v>-0.0505404410794741</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6715</v>
+        <v>6570</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>463.4202825676861</v>
+        <v>584.5426196577403</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>363.5</v>
+        <v>57.3</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>47.29255753055375</v>
+        <v>62.78642047667233</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>11.21529419691228</v>
+        <v>17.51839189660703</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.4688925881836271</v>
+        <v>2.821798166333596</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>1.714932397652252</v>
+        <v>1.020147977210087</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6830</v>
+        <v>6651</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>453.4382362107434</v>
+        <v>569.8512544222294</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>424.5</v>
+        <v>135</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>52.54861417169353</v>
+        <v>55.2073267495169</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>21.29932834693594</v>
+        <v>21.67273944619703</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.119607925823429</v>
+        <v>2.739427404341888</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>15.16503674177781</v>
+        <v>2.065680453017155</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6533</v>
+        <v>6708</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>447.4846734611374</v>
+        <v>567.7426857563656</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>250</v>
+        <v>38.8</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>63.32615909617144</v>
+        <v>51.82418142691544</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>17.84670684157508</v>
+        <v>13.21736218561355</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>3.13588276451926</v>
+        <v>0.3136627576445495</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>3.770773791979233</v>
+        <v>0.6951912532277955</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6743</v>
+        <v>6821</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>437.5575186325199</v>
+        <v>549.7721629012108</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>25.95</v>
+        <v>42.2</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>33.87861410110625</v>
+        <v>39.30309976830468</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>30.65643176615675</v>
+        <v>32.25931406786383</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.8234789719637171</v>
+        <v>0.4726612092843516</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.5587045831037137</v>
+        <v>0.7516924578296411</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6561</v>
+        <v>6684</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>433.7076490833803</v>
+        <v>546.0049317990571</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>327.5</v>
+        <v>50.2</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>49.0884234657758</v>
+        <v>51.55659956406806</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>16.62347082415516</v>
+        <v>16.81503294795015</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.5880489855703774</v>
+        <v>1.238054269529925</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>1.208785345212072</v>
+        <v>0.1866763663144728</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6834</v>
+        <v>6534</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>天二科技</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>433.5071841860943</v>
+        <v>542.5676561431853</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>96.59999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>51.42995958715492</v>
+        <v>54.26555904583456</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>18.11742300721276</v>
+        <v>23.65710296551155</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.088022397359117</v>
+        <v>1.529125061183476</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.2480144407518252</v>
+        <v>0.157373213808993</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6680</v>
+        <v>6789</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>432.1101223172679</v>
+        <v>540.558020671125</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>52.9</v>
+        <v>441.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>51.35654851602799</v>
+        <v>45.60821881364068</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>8.928063920683451</v>
+        <v>22.20721067968122</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.8490717286048675</v>
+        <v>0.8306212272732345</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,48 +1736,48 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-1.648866142513686</v>
+        <v>0.7751631651231854</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6689</v>
+        <v>6806</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>423.2327605734614</v>
+        <v>528.7768356926886</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>64.09999999999999</v>
+        <v>3.51</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G25" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>58.1748589731627</v>
+        <v>31.69502831466412</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>24.78905494688414</v>
+        <v>32.5931975692691</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.359868348421285</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.6793548770186604</v>
+        <v>0.4112821443334762</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6756</v>
+        <v>6763</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>407.6224378131971</v>
+        <v>528.6518570733527</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>99.90000000000001</v>
+        <v>43.35</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>54.80601789098797</v>
+        <v>50.96655679327223</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>18.41246145425619</v>
+        <v>30.24755573268313</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.6046125239328692</v>
+        <v>0.7146723558587027</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>1.074441310961462</v>
+        <v>0.3432725437155679</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6517</v>
+        <v>6672</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>402.9592611202101</v>
+        <v>519.6551418881993</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>62</v>
+        <v>251.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>43.65105831595943</v>
+        <v>56.67183179011068</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>17.74264075525872</v>
+        <v>22.66951128365132</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.1284796058816047</v>
+        <v>2.069419210418419</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.4950825195650075</v>
+        <v>3.476117446306505</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6494</v>
+        <v>6669</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>402.5202926201114</v>
+        <v>511.6128318963861</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>55.2</v>
+        <v>6010</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>54.1229302849265</v>
+        <v>60.0720042164613</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>27.54430289878499</v>
+        <v>19.81404541536655</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.14580192141777</v>
+        <v>0.8392590884643881</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.9095012201500574</v>
+        <v>78.62252026483554</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6658</v>
+        <v>6640</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>382.8295496624563</v>
+        <v>485.7200540579751</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>161.5</v>
+        <v>1005</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>49.57803870758161</v>
+        <v>54.59927404791888</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>23.76831546778813</v>
+        <v>20.21834003709472</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.7615987252108752</v>
+        <v>0.2956184699271068</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>2.208044636336305</v>
+        <v>20.53216758736876</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6691</v>
+        <v>6584</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>381.3977196089454</v>
+        <v>469.236949088452</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>732</v>
+        <v>522</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>56.39326079237441</v>
+        <v>46.18266784822475</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>16.12405063835193</v>
+        <v>30.31428625478637</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.7817796276097244</v>
+        <v>3.581754449205871</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>6.3943927806036</v>
+        <v>7.870487465498378</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6679</v>
+        <v>6742</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>369.2154689917006</v>
+        <v>468.4734612140247</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>215.5</v>
+        <v>44.1</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>43.50356665864479</v>
+        <v>40.82155755577556</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>31.37443742697766</v>
+        <v>21.68416843291506</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.7293921328468287</v>
+        <v>0.3084014009874118</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>2.322547877028937</v>
+        <v>0.5583314277996085</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6591</v>
+        <v>6805</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>357.2464052793781</v>
+        <v>467.7563613200151</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>44.9</v>
+        <v>1755</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>42.13820941058614</v>
+        <v>61.11310339296048</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45.03423550294112</v>
+        <v>30.83188965682062</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.143389778792955</v>
+        <v>1.860807352615913</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.4851264654756431</v>
+        <v>58.4128392384233</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6664</v>
+        <v>6788</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>348.442314200225</v>
+        <v>463.7194009541718</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>47.45542651341767</v>
+        <v>47.91640756928628</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>25.70798519345708</v>
+        <v>30.55004940999836</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.7454550082529414</v>
+        <v>0.614501683823488</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>1.261714691823794</v>
+        <v>5.132820348074866</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6556</v>
+        <v>6715</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>341</v>
+        <v>463.4202825676861</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>61.7</v>
+        <v>363.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>34.5926465168049</v>
+        <v>47.29255753055375</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>24.57604318797957</v>
+        <v>11.21529419691228</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>8.973581920851069</v>
+        <v>0.4688925881836271</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.1846656717517687</v>
+        <v>1.714932397652252</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6548</v>
+        <v>6829</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>336.6128649838843</v>
+        <v>459.3702725398588</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>75.7</v>
+        <v>200</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>53.05372729290665</v>
+        <v>51.05049877445995</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>19.98922929557009</v>
+        <v>17.61169749460068</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.6025674412759904</v>
+        <v>0.5689606547922962</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>1.19829039312493</v>
+        <v>1.502692858738342</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6799</v>
+        <v>6830</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>334.0242334417147</v>
+        <v>453.4382362107434</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>88</v>
+        <v>424.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>51.70061265124654</v>
+        <v>52.54861417169353</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>24.1331473169051</v>
+        <v>21.29932834693594</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.5210397605411677</v>
+        <v>1.119607925823429</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>1.525475232754612</v>
+        <v>15.16503674177781</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6588</v>
+        <v>6533</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>329.377052895135</v>
+        <v>447.4846734611374</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>90.5</v>
+        <v>250</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>52.17663244556365</v>
+        <v>63.32615909617144</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>19.66415085566471</v>
+        <v>17.84670684157508</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.4659584938125662</v>
+        <v>3.13588276451926</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>1.975970167190084</v>
+        <v>3.770773791979233</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6831</v>
+        <v>6720</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>327.7859982476213</v>
+        <v>438.3484706789851</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>619</v>
+        <v>138.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>47.22838285476606</v>
+        <v>50.82008206964079</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>23.85039667755416</v>
+        <v>29.42633325446777</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.92311151391005</v>
+        <v>0.655303744575668</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>9.930812126126725</v>
+        <v>0.5788071403539399</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6719</v>
+        <v>6743</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>325.9158525771313</v>
+        <v>437.5575186325199</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>205.5</v>
+        <v>25.95</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>40.82978142623313</v>
+        <v>33.87861410110625</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>20.79154253108725</v>
+        <v>30.65643176615675</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.026644398199289</v>
+        <v>0.8234789719637171</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.1702043061906515</v>
+        <v>-0.5587045831037137</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6577</v>
+        <v>6505</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>323.5857798095538</v>
+        <v>434.3654160374697</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>80.3</v>
+        <v>69</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>51.31890801893034</v>
+        <v>49.12673505215231</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>23.16408226615743</v>
+        <v>29.75468960838772</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.1266768507117398</v>
+        <v>0.419620588008366</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.3933678215734115</v>
+        <v>-1.804791900622028</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6770</v>
+        <v>6561</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>314.947886614597</v>
+        <v>433.7076490833803</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>67.59999999999999</v>
+        <v>327.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>53.55467541253191</v>
+        <v>49.0884234657758</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>16.20563895511379</v>
+        <v>16.62347082415516</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.169070819550472</v>
+        <v>0.5880489855703774</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>1.266537678945586</v>
+        <v>1.208785345212072</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6526</v>
+        <v>6834</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>313.9320709299399</v>
+        <v>433.5071841860943</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>627</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>54.46587496093099</v>
+        <v>51.42995958715492</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>18.71173356855546</v>
+        <v>18.11742300721276</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.5119133710669493</v>
+        <v>1.088022397359117</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>12.25517051224604</v>
+        <v>0.2480144407518252</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6512</v>
+        <v>6680</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>306.7794053218618</v>
+        <v>432.1101223172679</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>20.15</v>
+        <v>52.9</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>52.88827898383956</v>
+        <v>51.35654851602799</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>9.516375216289369</v>
+        <v>8.928063920683451</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.0453247302729</v>
+        <v>0.8490717286048675</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,7 +2743,7 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.5929995743408738</v>
+        <v>-1.648866142513686</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2753,21 +2753,21 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6641</v>
+        <v>6605</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>304.6382874993881</v>
+        <v>423.8067909385865</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>18.2</v>
+        <v>133.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>56.43482678571636</v>
+        <v>48.66613505665759</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>12.00180458616351</v>
+        <v>13.69023809512585</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.1768953973291743</v>
+        <v>2.832803818943578</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.083393593295577</v>
+        <v>0.7952693072369628</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6525</v>
+        <v>6689</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>302.9680112976309</v>
+        <v>423.2327605734614</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>142</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>48.54244158966806</v>
+        <v>58.1748589731627</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>22.13916893059711</v>
+        <v>24.78905494688414</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.5780713410641339</v>
+        <v>1.359868348421285</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.6126071199251202</v>
+        <v>0.6793548770186604</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6579</v>
+        <v>6727</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>亞泰金屬</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>297.1238093422038</v>
+        <v>416.5573216363507</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>164.5</v>
+        <v>388</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>49.98277258133356</v>
+        <v>50.23599132197263</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>14.21627861852767</v>
+        <v>15.79112206346012</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.464210850067146</v>
+        <v>1.212936839465476</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.4912583213197818</v>
+        <v>8.790721343260955</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6835</v>
+        <v>6550</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>291.7637366865634</v>
+        <v>410.5408898117086</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>31</v>
+        <v>11.25</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>38.74277447112021</v>
+        <v>37.72336004835542</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>40.4866736066228</v>
+        <v>25.85447077230404</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.5747743482189597</v>
+        <v>0.6847241090145594</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.1700125172537807</v>
+        <v>0.0228326553656625</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6722</v>
+        <v>6756</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>290.4601890576815</v>
+        <v>407.6224378131971</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>33.25</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>41.43794222196013</v>
+        <v>54.80601789098797</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45.09035858844592</v>
+        <v>18.41246145425619</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.6582239260824728</v>
+        <v>0.6046125239328692</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.0453051647860042</v>
+        <v>1.074441310961462</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6683</v>
+        <v>6517</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>286.538427429983</v>
+        <v>402.9592611202101</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>1230</v>
+        <v>62</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>48.2745948886829</v>
+        <v>43.65105831595943</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>28.25725879420688</v>
+        <v>17.74264075525872</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.4899732956481283</v>
+        <v>0.1284796058816047</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>31.4348537002561</v>
+        <v>-0.4950825195650075</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6531</v>
+        <v>6494</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>284.7992152405097</v>
+        <v>402.5202926201114</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>923</v>
+        <v>55.2</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>55.53775567986045</v>
+        <v>54.1229302849265</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>17.9383876361415</v>
+        <v>27.54430289878499</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.776806020075897</v>
+        <v>1.14580192141777</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>26.79131172666612</v>
+        <v>0.9095012201500574</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6613</v>
+        <v>6658</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>278.7082956743713</v>
+        <v>382.8295496624563</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>267</v>
+        <v>161.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>39.02089114142221</v>
+        <v>49.57803870758161</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>17.92466641318843</v>
+        <v>23.76831546778813</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.295821904755391</v>
+        <v>0.7615987252108752</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-2.564751388353312</v>
+        <v>2.208044636336305</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6546</v>
+        <v>6691</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>276.6720293204235</v>
+        <v>381.3977196089454</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>61.1</v>
+        <v>732</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>48.6918563128969</v>
+        <v>56.39326079237441</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>34.25128176075999</v>
+        <v>16.12405063835193</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.4540382745166306</v>
+        <v>0.7817796276097244</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.8710308901620962</v>
+        <v>6.3943927806036</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6568</v>
+        <v>6541</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>253.4327049767064</v>
+        <v>376.8559461019801</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>139.5</v>
+        <v>38.8</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>44.11459787240925</v>
+        <v>49.35901856634108</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>50.3952196306465</v>
+        <v>9.71640055352052</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.5120552148809838</v>
+        <v>0.634720209292394</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>2.265521062470729</v>
+        <v>0.0365724753294625</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6667</v>
+        <v>6679</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>252.4384138177306</v>
+        <v>369.2154689917006</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>235.5</v>
+        <v>215.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>45.71064707908463</v>
+        <v>43.50356665864479</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>26.92820647933205</v>
+        <v>31.37443742697766</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.8239079445400816</v>
+        <v>0.7293921328468287</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>1.098253347595543</v>
+        <v>2.322547877028937</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6581</v>
+        <v>6692</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>248.2253586697184</v>
+        <v>359.8501039559089</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>108</v>
+        <v>24.25</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>49.67379398493452</v>
+        <v>52.26106510648049</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>13.01856406597112</v>
+        <v>11.43825607522764</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.3520176135133184</v>
+        <v>3.244331776378185</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0219361556607685</v>
+        <v>0.5307021697131324</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6515</v>
+        <v>6591</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>241.0314674116884</v>
+        <v>357.2464052793781</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>6830</v>
+        <v>44.9</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>48.71305714719616</v>
+        <v>42.13820941058614</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>19.23198677474299</v>
+        <v>45.03423550294112</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.9790195446006202</v>
+        <v>1.143389778792955</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>181.6138323572908</v>
+        <v>0.4851264654756431</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6698</v>
+        <v>6664</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>235.1009942776442</v>
+        <v>348.442314200225</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>34.05</v>
+        <v>348</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>44.76379528547555</v>
+        <v>47.45542651341767</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>23.3107845556375</v>
+        <v>25.70798519345708</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.5893334830166511</v>
+        <v>0.7454550082529414</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.2970275502286945</v>
+        <v>1.261714691823794</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6488</v>
+        <v>6556</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>226.296324417609</v>
+        <v>341</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>854</v>
+        <v>61.7</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,49 +3520,49 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>40.00740011950307</v>
+        <v>34.5926465168049</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>19.6361494784886</v>
+        <v>24.57604318797957</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.6090360424699359</v>
+        <v>8.973581920851069</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-27.16885309080623</v>
+        <v>0.1846656717517687</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6654</v>
+        <v>6548</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>224.6346304023602</v>
+        <v>336.6128649838843</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>175.5</v>
+        <v>75.7</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>52.30623216854402</v>
+        <v>53.05372729290665</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>20.35072611833792</v>
+        <v>19.98922929557009</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.5443752742378344</v>
+        <v>0.6025674412759904</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.8049146976001036</v>
+        <v>1.19829039312493</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6695</v>
+        <v>6799</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>223.9700088630154</v>
+        <v>334.0242334417147</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>49.05</v>
+        <v>88</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>42.38783163284979</v>
+        <v>51.70061265124654</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>16.84054063700665</v>
+        <v>24.1331473169051</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.5859369776776999</v>
+        <v>0.5210397605411677</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.04727762318667</v>
+        <v>1.525475232754612</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6597</v>
+        <v>6582</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>215.8405061488688</v>
+        <v>333.6763982399528</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>67.8</v>
+        <v>32.1</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>52.56550927441516</v>
+        <v>50.69796412934451</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>9.227910220942441</v>
+        <v>17.04598918768167</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>2.222963075213416</v>
+        <v>0.7245360937738936</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>1.657113472402883</v>
+        <v>-0.0357494923945771</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6674</v>
+        <v>6588</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>211.4543449681333</v>
+        <v>329.377052895135</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>15.15</v>
+        <v>90.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>33.09777697734876</v>
+        <v>52.17663244556365</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>27.94371380273006</v>
+        <v>19.66415085566471</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.233427896138704</v>
+        <v>0.4659584938125662</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.0109324870091924</v>
+        <v>1.975970167190084</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6485</v>
+        <v>6831</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>210.1515967327581</v>
+        <v>327.7859982476213</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>65.2</v>
+        <v>619</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>46.58153637139367</v>
+        <v>47.22838285476606</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>31.92566440614958</v>
+        <v>23.85039667755416</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.8886209377032902</v>
+        <v>0.92311151391005</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>1.451334781405931</v>
+        <v>9.930812126126725</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6560</v>
+        <v>6719</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>208.2895459900261</v>
+        <v>325.9158525771313</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>32.75</v>
+        <v>205.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>42.6656646377571</v>
+        <v>40.82978142623313</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>23.55610304861302</v>
+        <v>20.79154253108725</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.09574777521272169</v>
+        <v>1.026644398199289</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.2164267139628419</v>
+        <v>-0.1702043061906515</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6486</v>
+        <v>6577</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>205.11694768226</v>
+        <v>323.5857798095538</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>74.8</v>
+        <v>80.3</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>37.32295600264841</v>
+        <v>51.31890801893034</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>20.93066759831938</v>
+        <v>23.16408226615743</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.4384345853634585</v>
+        <v>0.1266768507117398</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.0291627746541869</v>
+        <v>-0.3933678215734115</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6776</v>
+        <v>6770</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>199.3388245766569</v>
+        <v>314.947886614597</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>54</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>47.18497562275842</v>
+        <v>53.55467541253191</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>21.12908600125668</v>
+        <v>16.20563895511379</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.6309677549372419</v>
+        <v>1.169070819550472</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.1513933882284058</v>
+        <v>1.266537678945586</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6706</v>
+        <v>6526</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>195.4078662588853</v>
+        <v>313.9320709299399</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>115</v>
+        <v>627</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>47.36422328239001</v>
+        <v>54.46587496093099</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>27.9360274930259</v>
+        <v>18.71173356855546</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.400283400510497</v>
+        <v>0.5119133710669493</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>3.154285057340575</v>
+        <v>12.25517051224604</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6668</v>
+        <v>6512</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>186.9074690674686</v>
+        <v>306.7794053218618</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>35.25</v>
+        <v>20.15</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>47.20786546979786</v>
+        <v>52.88827898383956</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>14.09140970435063</v>
+        <v>9.516375216289369</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3209328948822644</v>
+        <v>1.0453247302729</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.1986078361931164</v>
+        <v>-0.5929995743408738</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6624</v>
+        <v>6690</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>182.9192891707028</v>
+        <v>305.7510537599638</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>43.55</v>
+        <v>164</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>54.1956178298716</v>
+        <v>49.94585251032228</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>10.31840855293046</v>
+        <v>20.27595202610962</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.0808055944507439</v>
+        <v>0.4089780143845499</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>3.456389985290163</v>
+        <v>0.7435820086444587</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6792</v>
+        <v>6641</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>181.4577717824017</v>
+        <v>304.6382874993881</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>58.1</v>
+        <v>18.2</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>53.53094301456269</v>
+        <v>56.43482678571636</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>20.83237706136118</v>
+        <v>12.00180458616351</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.1071657777679421</v>
+        <v>0.1768953973291743</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.9151082857450872</v>
+        <v>0.083393593295577</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, cci_momentum</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6552</v>
+        <v>6525</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>168.5981297540415</v>
+        <v>302.9680112976309</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>24.9</v>
+        <v>142</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>42.38434697611292</v>
+        <v>48.54244158966806</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>22.7585018338222</v>
+        <v>22.13916893059711</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.259430816537764</v>
+        <v>0.5780713410641339</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.191439221867006</v>
+        <v>-0.6126071199251202</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6498</v>
+        <v>6579</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>166.1113844479647</v>
+        <v>297.1238093422038</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>77</v>
+        <v>164.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>43.16491929246962</v>
+        <v>49.98277258133356</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>38.13070991314</v>
+        <v>14.21627861852767</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.8679145084146477</v>
+        <v>1.464210850067146</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.8198042544683419</v>
+        <v>0.4912583213197818</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6573</v>
+        <v>6835</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>163.1716928791651</v>
+        <v>291.7637366865634</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>16.95</v>
+        <v>31</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>42.60033215073253</v>
+        <v>38.74277447112021</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>16.91018142212874</v>
+        <v>40.4866736066228</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.5594342595761482</v>
+        <v>0.5747743482189597</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.2575969118523213</v>
+        <v>0.1700125172537807</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6643</v>
+        <v>6725</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>158.3184728606389</v>
+        <v>291.6591235557641</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>441</v>
+        <v>247.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>51.4404446531714</v>
+        <v>36.95481889378157</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>16.8644077092416</v>
+        <v>22.19511074119149</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.6067073503653335</v>
+        <v>0.6034485681140004</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>1</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>7.946861437298072</v>
+        <v>-2.024272536679021</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6771</v>
+        <v>6722</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>142.8745263239954</v>
+        <v>290.4601890576815</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>38</v>
+        <v>33.25</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>39.90102792412294</v>
+        <v>41.43794222196013</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>13.84143715119434</v>
+        <v>45.09035858844592</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.307740811853606</v>
+        <v>0.6582239260824728</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,64 +4439,2025 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.07260361763226519</v>
+        <v>0.0453051647860042</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
+        <v>6655</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>科定</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>287.1063888918754</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>48.39343386150986</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>5.682956899158487</v>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>0.3740984386145676</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N76" s="2" t="n">
+        <v>0.014379698632841</v>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>6683</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>雍智科技</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>286.538427429983</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>1230</v>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>48.2745948886829</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>28.25725879420688</v>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>0.4899732956481283</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N77" s="2" t="n">
+        <v>31.4348537002561</v>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>6531</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>愛普*</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>284.7992152405097</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>923</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>55.53775567986045</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>17.9383876361415</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>1.776806020075897</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N78" s="2" t="n">
+        <v>26.79131172666612</v>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>6613</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>朋億*</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>278.7082956743713</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>267</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>39.02089114142221</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>17.92466641318843</v>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>1.295821904755391</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N79" s="2" t="n">
+        <v>-2.564751388353312</v>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>6546</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>正基</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>276.6720293204235</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>48.6918563128969</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>34.25128176075999</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>0.4540382745166306</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>0.8710308901620962</v>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>6741</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>91APP*-KY</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>257.8532216262795</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>44.16510419880507</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>28.2945105819129</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>1.341542352475842</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>0.2703920026344735</v>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>6735</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>美達科技</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>255.0384157920361</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>40.91147710545035</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>29.08415966131303</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>1.336062356434631</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>1.377746177082622</v>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>6568</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>宏觀</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>253.4327049767064</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>44.11459787240925</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>50.3952196306465</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>0.5120552148809838</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N83" s="2" t="n">
+        <v>2.265521062470729</v>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, adx_trending, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>6667</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>信紘科</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>252.4384138177306</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>235.5</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>45.71064707908463</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>26.92820647933205</v>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>0.8239079445400816</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N84" s="2" t="n">
+        <v>1.098253347595543</v>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>6581</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>鋼聯</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>248.2253586697184</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>49.67379398493452</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>13.01856406597112</v>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>0.3520176135133184</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N85" s="2" t="n">
+        <v>0.0219361556607685</v>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>6515</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>241.0314674116884</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>6830</v>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>48.71305714719616</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>19.23198677474299</v>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>0.9790195446006202</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N86" s="2" t="n">
+        <v>181.6138323572908</v>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>6803</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>崑鼎</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>238.6034071093427</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>271.5</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>43.62915178490819</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>36.92136146419063</v>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>0.970904696175992</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>0.5411314164166452</v>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>6698</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>旭暉應材</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>235.1009942776442</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>44.76379528547555</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>23.3107845556375</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>0.5893334830166511</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N88" s="2" t="n">
+        <v>0.2970275502286945</v>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>6488</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>環球晶</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>226.296324417609</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>854</v>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>40.00740011950307</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>19.6361494784886</v>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>0.6090360424699359</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N89" s="2" t="n">
+        <v>-27.16885309080623</v>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>6654</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>天正國際</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>224.6346304023602</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>175.5</v>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>52.30623216854402</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>20.35072611833792</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>0.5443752742378344</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N90" s="2" t="n">
+        <v>0.8049146976001036</v>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>6695</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>芯鼎</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>223.9700088630154</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>49.05</v>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>42.38783163284979</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>16.84054063700665</v>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>0.5859369776776999</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N91" s="2" t="n">
+        <v>-0.04727762318667</v>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>6823</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>濾能</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>222.3170877585412</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>48.09788649260577</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>11.80738444797733</v>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>0.8317766514749244</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N92" s="2" t="n">
+        <v>0.5813705906331375</v>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>6597</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>立誠</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>215.8405061488688</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>52.56550927441516</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>9.227910220942441</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>2.222963075213416</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N93" s="2" t="n">
+        <v>1.657113472402883</v>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>6645</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>金萬林-創</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>215.1127092286683</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>42.2884600426394</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>23.48003296529696</v>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>0.2648340152809227</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N94" s="2" t="n">
+        <v>-0.0070743341418275</v>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>6732</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>昇佳電子</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>214.5664754355426</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>155.5</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>40.31730239668176</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>21.10849629340524</v>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>0.3001612682267133</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N95" s="2" t="n">
+        <v>-1.886577687072621</v>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>6674</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>鋐寶科技</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>211.4543449681333</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>15.15</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>33.09777697734876</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>27.94371380273006</v>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>1.233427896138704</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N96" s="2" t="n">
+        <v>-0.0109324870091924</v>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>6485</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>點序</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>210.1515967327581</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>46.58153637139367</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>31.92566440614958</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>0.8886209377032902</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N97" s="2" t="n">
+        <v>1.451334781405931</v>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, adx_trending, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>6560</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>欣普羅</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>208.2895459900261</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>32.75</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>42.6656646377571</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>23.55610304861302</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>0.09574777521272169</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>0.2164267139628419</v>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>6486</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>互動</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>205.11694768226</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>37.32295600264841</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>20.93066759831938</v>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>0.4384345853634585</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N99" s="2" t="n">
+        <v>-0.0291627746541869</v>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>6776</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>展碁國際</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>199.3388245766569</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>47.18497562275842</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>21.12908600125668</v>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>0.6309677549372419</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>0.1513933882284058</v>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>6706</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>惠特</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>195.4078662588853</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>47.36422328239001</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>27.9360274930259</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>1.400283400510497</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N101" s="2" t="n">
+        <v>3.154285057340575</v>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>6668</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>中揚光</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>186.9074690674685</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>35.25</v>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>47.20786546979786</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>14.09140970435063</v>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>0.3209328948822644</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N102" s="2" t="n">
+        <v>0.1986078361931164</v>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>6624</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>萬年清</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>182.9192891707028</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>54.1956178298716</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>10.31840855293046</v>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>0.0808055944507439</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N103" s="2" t="n">
+        <v>3.456389985290163</v>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>6792</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>詠業</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>181.4577717824017</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>53.53094301456269</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>20.83237706136118</v>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>0.1071657777679421</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N104" s="2" t="n">
+        <v>0.9151082857450872</v>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, adx_trending, cci_momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>6552</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>易華電</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>168.5981297540415</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>42.38434697611292</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>22.7585018338222</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>0.259430816537764</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>0.191439221867006</v>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>6498</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>久禾光</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>166.1113844479647</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>43.16491929246962</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>38.13070991314</v>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>0.8679145084146477</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N106" s="2" t="n">
+        <v>0.8198042544683419</v>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>6573</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>虹揚-KY</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>163.1716928791651</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>42.60033215073253</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>16.91018142212874</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>0.5594342595761482</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N107" s="2" t="n">
+        <v>-0.2575969118523213</v>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>6643</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>M31</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>158.3184728606389</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>441</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>51.4404446531714</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>16.8644077092416</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>0.6067073503653335</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N108" s="2" t="n">
+        <v>7.946861437298072</v>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, liquidity_ok, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>6771</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>平和環保-創</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>142.8745263239954</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>39.90102792412294</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>13.84143715119434</v>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>1.307740811853606</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>0.07260361763226519</v>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
         <v>6558</v>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>興能高</t>
         </is>
       </c>
-      <c r="C76" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D76" s="2" t="n">
+      <c r="C110" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D110" s="2" t="n">
         <v>132.9799379394085</v>
       </c>
-      <c r="E76" s="2" t="n">
+      <c r="E110" s="2" t="n">
         <v>26.75</v>
       </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H76" s="2" t="n">
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H110" s="2" t="n">
         <v>49.35985312135943</v>
       </c>
-      <c r="I76" s="2" t="n">
+      <c r="I110" s="2" t="n">
         <v>31.78033287105508</v>
       </c>
-      <c r="J76" s="2" t="n">
+      <c r="J110" s="2" t="n">
         <v>0.9041300013487308</v>
       </c>
-      <c r="K76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N76" s="2" t="n">
+      <c r="K110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N110" s="2" t="n">
         <v>0.2548989916106241</v>
       </c>
-      <c r="O76" s="2" t="inlineStr">
+      <c r="O110" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>6592</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>和潤企業</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>126.7863299962344</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>48.91672072180006</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>12.90889897407236</v>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>0.4326429627152402</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>0.09036296809479689</v>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>6614</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>資拓宏宇</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>106.0179244137837</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>35.85</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>31.111760642823</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>18.15358759528153</v>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>0.5232085546258598</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N112" s="2" t="n">
+        <v>-0.1376631880105543</v>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>6625</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>必應</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>91.20556690867112</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>52.7801239412233</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>16.08133511582697</v>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>1.014605467866428</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N113" s="2" t="n">
+        <v>0.2843525709206014</v>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>

--- a/output/full_scan/batch_seq7_2026-08-10.xlsx
+++ b/output/full_scan/batch_seq7_2026-08-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O113"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6589</v>
+        <v>6782</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>視陽</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>903.1291122950096</v>
+        <v>960.1876249289984</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>50.7</v>
+        <v>214</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>63.20820428277012</v>
+        <v>66.01281568602366</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>20.28430258577195</v>
+        <v>25.55600172008031</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>2.224597440910823</v>
+        <v>1.618762492899835</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.4221706655771498</v>
+        <v>3.678348173758471</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6606</v>
+        <v>6589</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>859.2585208683897</v>
+        <v>903.1291122950096</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>26.4</v>
+        <v>50.7</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>64.9322162182639</v>
+        <v>63.20820428277012</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>11.32805055959344</v>
+        <v>20.28430258577195</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.33234245213</v>
+        <v>2.224597440910823</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.0184664548661789</v>
+        <v>0.4221706655771498</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6716</v>
+        <v>6606</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>808.8507934837611</v>
+        <v>859.2585208683897</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>105</v>
+        <v>26.4</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>66.65619037802345</v>
+        <v>64.9322162182639</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>21.99245011801612</v>
+        <v>11.32805055959344</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.408137471200302</v>
+        <v>1.33234245213</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>2.825541977084809</v>
+        <v>0.0184664548661789</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6491</v>
+        <v>6716</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>763.6151179059989</v>
+        <v>808.8507934837611</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>379</v>
+        <v>105</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>65.97135344201988</v>
+        <v>66.65619037802345</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>24.23052685244127</v>
+        <v>21.99245011801612</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.9238484290684073</v>
+        <v>1.408137471200302</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>4.415376844735866</v>
+        <v>2.825541977084809</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6585</v>
+        <v>6491</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>759.1229721981631</v>
+        <v>763.6151179059989</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>117.5</v>
+        <v>379</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>47.42447050181128</v>
+        <v>65.97135344201988</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>19.77777410643681</v>
+        <v>24.23052685244127</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.738748160150335</v>
+        <v>0.9238484290684073</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.1322649076297377</v>
+        <v>4.415376844735866</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6811</v>
+        <v>6585</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>748.7586716265645</v>
+        <v>759.1229721981631</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>235</v>
+        <v>117.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>54.31271275553281</v>
+        <v>47.42447050181128</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>20.28575397640271</v>
+        <v>19.77777410643681</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.5415195298719717</v>
+        <v>1.738748160150335</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.4202800286211601</v>
+        <v>-0.1322649076297377</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6781</v>
+        <v>6811</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>719.8912550996769</v>
+        <v>748.7586716265645</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1195</v>
+        <v>235</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>63.66996250914878</v>
+        <v>54.31271275553281</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>21.99323176115009</v>
+        <v>20.28575397640271</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2.089125509967689</v>
+        <v>0.5415195298719717</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>32.35333156805501</v>
+        <v>0.4202800286211601</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6598</v>
+        <v>6781</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>710.5301595514918</v>
+        <v>719.8912550996769</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>29.4</v>
+        <v>1195</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>56.16138578541567</v>
+        <v>63.66996250914878</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>37.81218167631322</v>
+        <v>21.99323176115009</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.3585962222119435</v>
+        <v>2.089125509967689</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-0.0879665259676758</v>
+        <v>32.35333156805501</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6532</v>
+        <v>6753</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>龍德造船</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>697.5891083167379</v>
+        <v>712.2291274426832</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>83.5</v>
+        <v>142</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>61.98118191778797</v>
+        <v>54.7974471137344</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>30.72823203396104</v>
+        <v>18.30360133877879</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.653578451812226</v>
+        <v>1.122365272809679</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>2.656475657580986</v>
+        <v>-0.1973597681589906</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6510</v>
+        <v>6598</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>683.1425714737663</v>
+        <v>710.5301595514918</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2845</v>
+        <v>29.4</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,49 +1029,49 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>51.91621449396283</v>
+        <v>56.16138578541567</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>25.15402236835393</v>
+        <v>37.81218167631322</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.54779792100466</v>
+        <v>0.3585962222119435</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>58.225230001748</v>
+        <v>-0.0879665259676758</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6538</v>
+        <v>6532</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>倉和</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>679.0725445667794</v>
+        <v>697.5891083167379</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>145.5</v>
+        <v>83.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>55.34335939424123</v>
+        <v>61.98118191778797</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>22.83368063286276</v>
+        <v>30.72823203396104</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.5449581570377342</v>
+        <v>2.653578451812226</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.7470759547209362</v>
+        <v>2.656475657580986</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6693</v>
+        <v>6510</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>649.4159036416214</v>
+        <v>683.1425714737663</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>184</v>
+        <v>2845</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>50.38863430194367</v>
+        <v>51.91621449396283</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>26.94908635017923</v>
+        <v>25.15402236835393</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>3.328927515200341</v>
+        <v>1.54779792100466</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>1.716256404857681</v>
+        <v>58.225230001748</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong</t>
+          <t>volume_break, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6642</v>
+        <v>6538</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>628.6846060253871</v>
+        <v>679.0725445667794</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>83.3</v>
+        <v>145.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>60.2889815494212</v>
+        <v>55.34335939424123</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>17.20897975546421</v>
+        <v>22.83368063286276</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>4.284213476239731</v>
+        <v>0.5449581570377342</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>1.156990142525024</v>
+        <v>0.7470759547209362</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6761</v>
+        <v>6693</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>625.7448923331278</v>
+        <v>649.4159036416214</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>54.05048169608121</v>
+        <v>50.38863430194367</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>26.02804642597277</v>
+        <v>26.94908635017923</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>2.362822094468798</v>
+        <v>3.328927515200341</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>3.685602557869743</v>
+        <v>1.716256404857681</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6530</v>
+        <v>6642</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>612.5901958258647</v>
+        <v>628.6846060253871</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>82.5</v>
+        <v>83.3</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>55.3255704569258</v>
+        <v>60.2889815494212</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>23.70751846741007</v>
+        <v>17.20897975546421</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.819285779096404</v>
+        <v>4.284213476239731</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>1</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>2.232003913636197</v>
+        <v>1.156990142525024</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6504</v>
+        <v>6761</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>603.0976881410558</v>
+        <v>625.7448923331278</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>39</v>
+        <v>168</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>56.12879605314978</v>
+        <v>54.05048169608121</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>28.8372696995016</v>
+        <v>26.02804642597277</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.3446491781906637</v>
+        <v>2.362822094468798</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.0505404410794741</v>
+        <v>3.685602557869743</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6570</v>
+        <v>6530</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>584.5426196577403</v>
+        <v>612.5901958258647</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>57.3</v>
+        <v>82.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>62.78642047667233</v>
+        <v>55.3255704569258</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>17.51839189660703</v>
+        <v>23.70751846741007</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>2.821798166333596</v>
+        <v>1.819285779096404</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>1.020147977210087</v>
+        <v>2.232003913636197</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6651</v>
+        <v>6504</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>569.8512544222294</v>
+        <v>603.0976881410558</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>135</v>
+        <v>39</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>55.2073267495169</v>
+        <v>56.12879605314978</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>21.67273944619703</v>
+        <v>28.8372696995016</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2.739427404341888</v>
+        <v>0.3446491781906637</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>2.065680453017155</v>
+        <v>-0.0505404410794741</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6708</v>
+        <v>6807</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>峰源-KY</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>567.7426857563656</v>
+        <v>593.0114392871835</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>38.8</v>
+        <v>37.9</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>51.82418142691544</v>
+        <v>78.94256237876938</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>13.21736218561355</v>
+        <v>16.2922296525899</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.3136627576445495</v>
+        <v>0.3965604263811777</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.6951912532277955</v>
+        <v>0.3680542806757046</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend, williams_r_recovery, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6821</v>
+        <v>6570</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>549.7721629012108</v>
+        <v>584.5426196577403</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>42.2</v>
+        <v>57.3</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>39.30309976830468</v>
+        <v>62.78642047667233</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>32.25931406786383</v>
+        <v>17.51839189660703</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.4726612092843516</v>
+        <v>2.821798166333596</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.7516924578296411</v>
+        <v>1.020147977210087</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6684</v>
+        <v>6651</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>546.0049317990571</v>
+        <v>569.8512544222294</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>50.2</v>
+        <v>135</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>51.55659956406806</v>
+        <v>55.2073267495169</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>16.81503294795015</v>
+        <v>21.67273944619703</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.238054269529925</v>
+        <v>2.739427404341888</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.1866763663144728</v>
+        <v>2.065680453017155</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6534</v>
+        <v>6708</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>542.5676561431853</v>
+        <v>567.7426857563656</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>94.09999999999999</v>
+        <v>38.8</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>54.26555904583456</v>
+        <v>51.82418142691544</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>23.65710296551155</v>
+        <v>13.21736218561355</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.529125061183476</v>
+        <v>0.3136627576445495</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.157373213808993</v>
+        <v>0.6951912532277955</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6789</v>
+        <v>6666</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>羅麗芬-KY</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>540.558020671125</v>
+        <v>560.3756794568671</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>441.5</v>
+        <v>43.25</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>45.60821881364068</v>
+        <v>46.18406819702407</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>22.20721067968122</v>
+        <v>32.47999311729652</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.8306212272732345</v>
+        <v>0.4689437146963101</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,51 +1736,51 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.7751631651231854</v>
+        <v>-0.298163087406554</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6806</v>
+        <v>6821</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>528.7768356926886</v>
+        <v>549.7721629012108</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>3.51</v>
+        <v>42.2</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G25" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>31.69502831466412</v>
+        <v>39.30309976830468</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>32.5931975692691</v>
+        <v>32.25931406786383</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>0.4726612092843516</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.4112821443334762</v>
+        <v>0.7516924578296411</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6763</v>
+        <v>6684</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>528.6518570733527</v>
+        <v>546.0049317990571</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>43.35</v>
+        <v>50.2</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>50.96655679327223</v>
+        <v>51.55659956406806</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>30.24755573268313</v>
+        <v>16.81503294795015</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.7146723558587027</v>
+        <v>1.238054269529925</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.3432725437155679</v>
+        <v>0.1866763663144728</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6672</v>
+        <v>6534</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>519.6551418881993</v>
+        <v>542.5676561431853</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>251.5</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>56.67183179011068</v>
+        <v>54.26555904583456</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>22.66951128365132</v>
+        <v>23.65710296551155</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>2.069419210418419</v>
+        <v>1.529125061183476</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>3.476117446306505</v>
+        <v>0.157373213808993</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6669</v>
+        <v>6789</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>511.6128318963861</v>
+        <v>540.558020671125</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>6010</v>
+        <v>441.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>60.0720042164613</v>
+        <v>45.60821881364068</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>19.81404541536655</v>
+        <v>22.20721067968122</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.8392590884643881</v>
+        <v>0.8306212272732345</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,48 +1948,48 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>78.62252026483554</v>
+        <v>0.7751631651231854</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6640</v>
+        <v>6806</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>485.7200540579751</v>
+        <v>528.7768356926886</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1005</v>
+        <v>3.51</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G29" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>54.59927404791888</v>
+        <v>31.69502831466412</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>20.21834003709472</v>
+        <v>32.5931975692691</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.2956184699271068</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>20.53216758736876</v>
+        <v>0.4112821443334762</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6584</v>
+        <v>6763</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>469.236949088452</v>
+        <v>528.6518570733527</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>522</v>
+        <v>43.35</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>46.18266784822475</v>
+        <v>50.96655679327223</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>30.31428625478637</v>
+        <v>30.24755573268313</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>3.581754449205871</v>
+        <v>0.7146723558587027</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>7.870487465498378</v>
+        <v>0.3432725437155679</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6742</v>
+        <v>6672</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>468.4734612140247</v>
+        <v>519.6551418881993</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>44.1</v>
+        <v>251.5</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>40.82155755577556</v>
+        <v>56.67183179011068</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>21.68416843291506</v>
+        <v>22.66951128365132</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.3084014009874118</v>
+        <v>2.069419210418419</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.5583314277996085</v>
+        <v>3.476117446306505</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6805</v>
+        <v>6669</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>467.7563613200151</v>
+        <v>511.6128318963861</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1755</v>
+        <v>6010</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>61.11310339296048</v>
+        <v>60.0720042164613</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>30.83188965682062</v>
+        <v>19.81404541536655</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.860807352615913</v>
+        <v>0.8392590884643881</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>58.4128392384233</v>
+        <v>78.62252026483554</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6788</v>
+        <v>6796</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>晉弘</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>463.7194009541718</v>
+        <v>494.650318786276</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>355</v>
+        <v>59.8</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>47.91640756928628</v>
+        <v>57.32214159044644</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>30.55004940999836</v>
+        <v>20.11533584545269</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.614501683823488</v>
+        <v>0.97990016579925</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>5.132820348074866</v>
+        <v>0.2272096422298007</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
+          <t>macd_golden_cross, rsi_strong, market_above_ma60, hist_turn_positive, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6715</v>
+        <v>6640</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>463.4202825676861</v>
+        <v>485.7200540579751</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>363.5</v>
+        <v>1005</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>47.29255753055375</v>
+        <v>54.59927404791888</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>11.21529419691228</v>
+        <v>20.21834003709472</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.4688925881836271</v>
+        <v>0.2956184699271068</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>1.714932397652252</v>
+        <v>20.53216758736876</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6829</v>
+        <v>6584</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>459.3702725398588</v>
+        <v>469.236949088452</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>200</v>
+        <v>522</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>51.05049877445995</v>
+        <v>46.18266784822475</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>17.61169749460068</v>
+        <v>30.31428625478637</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.5689606547922962</v>
+        <v>3.581754449205871</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>1.502692858738342</v>
+        <v>7.870487465498378</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6830</v>
+        <v>6742</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>453.4382362107434</v>
+        <v>468.4734612140247</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>424.5</v>
+        <v>44.1</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>52.54861417169353</v>
+        <v>40.82155755577556</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>21.29932834693594</v>
+        <v>21.68416843291506</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.119607925823429</v>
+        <v>0.3084014009874118</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>15.16503674177781</v>
+        <v>0.5583314277996085</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6533</v>
+        <v>6805</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>447.4846734611374</v>
+        <v>467.7563613200151</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>250</v>
+        <v>1755</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>63.32615909617144</v>
+        <v>61.11310339296048</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>17.84670684157508</v>
+        <v>30.83188965682062</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>3.13588276451926</v>
+        <v>1.860807352615913</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>3.770773791979233</v>
+        <v>58.4128392384233</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6720</v>
+        <v>6788</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>438.3484706789851</v>
+        <v>463.7194009541718</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>138.5</v>
+        <v>355</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>50.82008206964079</v>
+        <v>47.91640756928628</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>29.42633325446777</v>
+        <v>30.55004940999836</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.655303744575668</v>
+        <v>0.614501683823488</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.5788071403539399</v>
+        <v>5.132820348074866</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, cci_momentum</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6743</v>
+        <v>6715</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>437.5575186325199</v>
+        <v>463.4202825676861</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>25.95</v>
+        <v>363.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>33.87861410110625</v>
+        <v>47.29255753055375</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>30.65643176615675</v>
+        <v>11.21529419691228</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.8234789719637171</v>
+        <v>0.4688925881836271</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.5587045831037137</v>
+        <v>1.714932397652252</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6505</v>
+        <v>6829</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>434.3654160374697</v>
+        <v>459.3702725398588</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>69</v>
+        <v>200</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>49.12673505215231</v>
+        <v>51.05049877445995</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>29.75468960838772</v>
+        <v>17.61169749460068</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.419620588008366</v>
+        <v>0.5689606547922962</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-1.804791900622028</v>
+        <v>1.502692858738342</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6561</v>
+        <v>6830</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>433.7076490833803</v>
+        <v>453.4382362107434</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>327.5</v>
+        <v>424.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>49.0884234657758</v>
+        <v>52.54861417169353</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>16.62347082415516</v>
+        <v>21.29932834693594</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.5880489855703774</v>
+        <v>1.119607925823429</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>1.208785345212072</v>
+        <v>15.16503674177781</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6834</v>
+        <v>6533</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>天二科技</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>433.5071841860943</v>
+        <v>447.4846734611374</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>96.59999999999999</v>
+        <v>250</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>51.42995958715492</v>
+        <v>63.32615909617144</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>18.11742300721276</v>
+        <v>17.84670684157508</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.088022397359117</v>
+        <v>3.13588276451926</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.2480144407518252</v>
+        <v>3.770773791979233</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6680</v>
+        <v>6720</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>432.1101223172679</v>
+        <v>438.3484706789851</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>52.9</v>
+        <v>138.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>51.35654851602799</v>
+        <v>50.82008206964079</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>8.928063920683451</v>
+        <v>29.42633325446777</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.8490717286048675</v>
+        <v>0.655303744575668</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-1.648866142513686</v>
+        <v>0.5788071403539399</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6605</v>
+        <v>6743</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>423.8067909385865</v>
+        <v>437.5575186325199</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>133.5</v>
+        <v>25.95</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>48.66613505665759</v>
+        <v>33.87861410110625</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>13.69023809512585</v>
+        <v>30.65643176615675</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>2.832803818943578</v>
+        <v>0.8234789719637171</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.7952693072369628</v>
+        <v>-0.5587045831037137</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6689</v>
+        <v>6505</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>423.2327605734614</v>
+        <v>434.3654160374697</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>64.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>58.1748589731627</v>
+        <v>49.12673505215231</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>24.78905494688414</v>
+        <v>29.75468960838772</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.359868348421285</v>
+        <v>0.419620588008366</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.6793548770186604</v>
+        <v>-1.804791900622028</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6727</v>
+        <v>6561</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>亞泰金屬</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>416.5573216363507</v>
+        <v>433.7076490833803</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>388</v>
+        <v>327.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>50.23599132197263</v>
+        <v>49.0884234657758</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>15.79112206346012</v>
+        <v>16.62347082415516</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.212936839465476</v>
+        <v>0.5880489855703774</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>8.790721343260955</v>
+        <v>1.208785345212072</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6550</v>
+        <v>6834</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>410.5408898117086</v>
+        <v>433.5071841860943</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>11.25</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>37.72336004835542</v>
+        <v>51.42995958715492</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>25.85447077230404</v>
+        <v>18.11742300721276</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.6847241090145594</v>
+        <v>1.088022397359117</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.0228326553656625</v>
+        <v>0.2480144407518252</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6756</v>
+        <v>6680</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>407.6224378131971</v>
+        <v>432.1101223172679</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>99.90000000000001</v>
+        <v>52.9</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>54.80601789098797</v>
+        <v>51.35654851602799</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>18.41246145425619</v>
+        <v>8.928063920683451</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.6046125239328692</v>
+        <v>0.8490717286048675</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>1.074441310961462</v>
+        <v>-1.648866142513686</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6517</v>
+        <v>6605</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>402.9592611202101</v>
+        <v>423.8067909385865</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>62</v>
+        <v>133.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>43.65105831595943</v>
+        <v>48.66613505665759</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>17.74264075525872</v>
+        <v>13.69023809512585</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.1284796058816047</v>
+        <v>2.832803818943578</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.4950825195650075</v>
+        <v>0.7952693072369628</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6494</v>
+        <v>6689</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>402.5202926201114</v>
+        <v>423.2327605734614</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>55.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>54.1229302849265</v>
+        <v>58.1748589731627</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>27.54430289878499</v>
+        <v>24.78905494688414</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.14580192141777</v>
+        <v>1.359868348421285</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.9095012201500574</v>
+        <v>0.6793548770186604</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6658</v>
+        <v>6727</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>亞泰金屬</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>382.8295496624563</v>
+        <v>416.5573216363507</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>161.5</v>
+        <v>388</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>49.57803870758161</v>
+        <v>50.23599132197263</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>23.76831546778813</v>
+        <v>15.79112206346012</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.7615987252108752</v>
+        <v>1.212936839465476</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>2.208044636336305</v>
+        <v>8.790721343260955</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6691</v>
+        <v>6550</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>381.3977196089454</v>
+        <v>410.5408898117086</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>732</v>
+        <v>11.25</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>56.39326079237441</v>
+        <v>37.72336004835542</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>16.12405063835193</v>
+        <v>25.85447077230404</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.7817796276097244</v>
+        <v>0.6847241090145594</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>6.3943927806036</v>
+        <v>0.0228326553656625</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6541</v>
+        <v>6756</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>376.8559461019801</v>
+        <v>407.6224378131971</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>38.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>49.35901856634108</v>
+        <v>54.80601789098797</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>9.71640055352052</v>
+        <v>18.41246145425619</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.634720209292394</v>
+        <v>0.6046125239328692</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.0365724753294625</v>
+        <v>1.074441310961462</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6679</v>
+        <v>6517</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>369.2154689917006</v>
+        <v>402.9592611202101</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>215.5</v>
+        <v>62</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>43.50356665864479</v>
+        <v>43.65105831595943</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>31.37443742697766</v>
+        <v>17.74264075525872</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.7293921328468287</v>
+        <v>0.1284796058816047</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>2.322547877028937</v>
+        <v>-0.4950825195650075</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6692</v>
+        <v>6494</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>359.8501039559089</v>
+        <v>402.5202926201114</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>24.25</v>
+        <v>55.2</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>52.26106510648049</v>
+        <v>54.1229302849265</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>11.43825607522764</v>
+        <v>27.54430289878499</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>3.244331776378185</v>
+        <v>1.14580192141777</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.5307021697131324</v>
+        <v>0.9095012201500574</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6591</v>
+        <v>6658</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>357.2464052793781</v>
+        <v>382.8295496624563</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>44.9</v>
+        <v>161.5</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>42.13820941058614</v>
+        <v>49.57803870758161</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45.03423550294112</v>
+        <v>23.76831546778813</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.143389778792955</v>
+        <v>0.7615987252108752</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.4851264654756431</v>
+        <v>2.208044636336305</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6664</v>
+        <v>6691</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>348.442314200225</v>
+        <v>381.3977196089454</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>348</v>
+        <v>732</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>47.45542651341767</v>
+        <v>56.39326079237441</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>25.70798519345708</v>
+        <v>16.12405063835193</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.7454550082529414</v>
+        <v>0.7817796276097244</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>1.261714691823794</v>
+        <v>6.3943927806036</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6556</v>
+        <v>6541</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>341</v>
+        <v>376.8559461019801</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>61.7</v>
+        <v>38.8</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>34.5926465168049</v>
+        <v>49.35901856634108</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>24.57604318797957</v>
+        <v>9.71640055352052</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>8.973581920851069</v>
+        <v>0.634720209292394</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.1846656717517687</v>
+        <v>0.0365724753294625</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6548</v>
+        <v>6679</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>336.6128649838843</v>
+        <v>369.2154689917006</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>75.7</v>
+        <v>215.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>53.05372729290665</v>
+        <v>43.50356665864479</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>19.98922929557009</v>
+        <v>31.37443742697766</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.6025674412759904</v>
+        <v>0.7293921328468287</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>1.19829039312493</v>
+        <v>2.322547877028937</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6799</v>
+        <v>6692</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>334.0242334417147</v>
+        <v>359.8501039559089</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>88</v>
+        <v>24.25</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>51.70061265124654</v>
+        <v>52.26106510648049</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>24.1331473169051</v>
+        <v>11.43825607522764</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.5210397605411677</v>
+        <v>3.244331776378185</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>1.525475232754612</v>
+        <v>0.5307021697131324</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6582</v>
+        <v>6591</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>333.6763982399528</v>
+        <v>357.2464052793781</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>32.1</v>
+        <v>44.9</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>50.69796412934451</v>
+        <v>42.13820941058614</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>17.04598918768167</v>
+        <v>45.03423550294112</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.7245360937738936</v>
+        <v>1.143389778792955</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.0357494923945771</v>
+        <v>0.4851264654756431</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6588</v>
+        <v>6664</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>329.377052895135</v>
+        <v>348.442314200225</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>90.5</v>
+        <v>348</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>52.17663244556365</v>
+        <v>47.45542651341767</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>19.66415085566471</v>
+        <v>25.70798519345708</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.4659584938125662</v>
+        <v>0.7454550082529414</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>1</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>1.975970167190084</v>
+        <v>1.261714691823794</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6831</v>
+        <v>6670</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>327.7859982476213</v>
+        <v>343.0914384989764</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>619</v>
+        <v>266.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,49 +3785,49 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>47.22838285476606</v>
+        <v>53.58976190942653</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>23.85039667755416</v>
+        <v>11.71880494431926</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.92311151391005</v>
+        <v>0.301248206087955</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>9.930812126126725</v>
+        <v>0.579237890237448</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6719</v>
+        <v>6556</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>325.9158525771313</v>
+        <v>341</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>205.5</v>
+        <v>61.7</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>40.82978142623313</v>
+        <v>34.5926465168049</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>20.79154253108725</v>
+        <v>24.57604318797957</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.026644398199289</v>
+        <v>8.973581920851069</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.1702043061906515</v>
+        <v>0.1846656717517687</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6577</v>
+        <v>6548</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>323.5857798095538</v>
+        <v>336.6128649838843</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>80.3</v>
+        <v>75.7</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>51.31890801893034</v>
+        <v>53.05372729290665</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>23.16408226615743</v>
+        <v>19.98922929557009</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.1266768507117398</v>
+        <v>0.6025674412759904</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>1</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.3933678215734115</v>
+        <v>1.19829039312493</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6770</v>
+        <v>6799</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>314.947886614597</v>
+        <v>334.0242334417147</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>67.59999999999999</v>
+        <v>88</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>53.55467541253191</v>
+        <v>51.70061265124654</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>16.20563895511379</v>
+        <v>24.1331473169051</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.169070819550472</v>
+        <v>0.5210397605411677</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>1.266537678945586</v>
+        <v>1.525475232754612</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6526</v>
+        <v>6582</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>313.9320709299399</v>
+        <v>333.6763982399528</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>627</v>
+        <v>32.1</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>54.46587496093099</v>
+        <v>50.69796412934451</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>18.71173356855546</v>
+        <v>17.04598918768167</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.5119133710669493</v>
+        <v>0.7245360937738936</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>12.25517051224604</v>
+        <v>-0.0357494923945771</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6512</v>
+        <v>6768</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>志強-KY</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>306.7794053218618</v>
+        <v>332.0837655169215</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>20.15</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>52.88827898383956</v>
+        <v>35.49738004222978</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>9.516375216289369</v>
+        <v>34.85998004930307</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.0453247302729</v>
+        <v>0.7981031938357406</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.5929995743408738</v>
+        <v>0.2466406569253871</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6690</v>
+        <v>6588</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>305.7510537599638</v>
+        <v>329.377052895135</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>164</v>
+        <v>90.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>49.94585251032228</v>
+        <v>52.17663244556365</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>20.27595202610962</v>
+        <v>19.66415085566471</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.4089780143845499</v>
+        <v>0.4659584938125662</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.7435820086444587</v>
+        <v>1.975970167190084</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6641</v>
+        <v>6831</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>304.6382874993881</v>
+        <v>327.7859982476213</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>18.2</v>
+        <v>619</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>56.43482678571636</v>
+        <v>47.22838285476606</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>12.00180458616351</v>
+        <v>23.85039667755416</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.1768953973291743</v>
+        <v>0.92311151391005</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.083393593295577</v>
+        <v>9.930812126126725</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6525</v>
+        <v>6719</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>302.9680112976309</v>
+        <v>325.9158525771313</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>142</v>
+        <v>205.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>48.54244158966806</v>
+        <v>40.82978142623313</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>22.13916893059711</v>
+        <v>20.79154253108725</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.5780713410641339</v>
+        <v>1.026644398199289</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.6126071199251202</v>
+        <v>-0.1702043061906515</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6579</v>
+        <v>6577</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>297.1238093422038</v>
+        <v>323.5857798095538</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>164.5</v>
+        <v>80.3</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>49.98277258133356</v>
+        <v>51.31890801893034</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>14.21627861852767</v>
+        <v>23.16408226615743</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.464210850067146</v>
+        <v>0.1266768507117398</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.4912583213197818</v>
+        <v>-0.3933678215734115</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6835</v>
+        <v>6770</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>291.7637366865634</v>
+        <v>314.947886614597</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>31</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>38.74277447112021</v>
+        <v>53.55467541253191</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>40.4866736066228</v>
+        <v>16.20563895511379</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.5747743482189597</v>
+        <v>1.169070819550472</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.1700125172537807</v>
+        <v>1.266537678945586</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6725</v>
+        <v>6526</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>291.6591235557641</v>
+        <v>313.9320709299399</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>247.5</v>
+        <v>627</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>36.95481889378157</v>
+        <v>54.46587496093099</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>22.19511074119149</v>
+        <v>18.71173356855546</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.6034485681140004</v>
+        <v>0.5119133710669493</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-2.024272536679021</v>
+        <v>12.25517051224604</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6722</v>
+        <v>6512</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>290.4601890576815</v>
+        <v>306.7794053218618</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>33.25</v>
+        <v>20.15</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>41.43794222196013</v>
+        <v>52.88827898383956</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>45.09035858844592</v>
+        <v>9.516375216289369</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.6582239260824728</v>
+        <v>1.0453247302729</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0453051647860042</v>
+        <v>-0.5929995743408738</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6655</v>
+        <v>6690</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>287.1063888918754</v>
+        <v>305.7510537599638</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>117.5</v>
+        <v>164</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>48.39343386150986</v>
+        <v>49.94585251032228</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>5.682956899158487</v>
+        <v>20.27595202610962</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.3740984386145676</v>
+        <v>0.4089780143845499</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.014379698632841</v>
+        <v>0.7435820086444587</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6683</v>
+        <v>6641</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>286.538427429983</v>
+        <v>304.6382874993881</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>1230</v>
+        <v>18.2</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>48.2745948886829</v>
+        <v>56.43482678571636</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>28.25725879420688</v>
+        <v>12.00180458616351</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.4899732956481283</v>
+        <v>0.1768953973291743</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>31.4348537002561</v>
+        <v>0.083393593295577</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6531</v>
+        <v>6525</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>284.7992152405097</v>
+        <v>302.9680112976309</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>923</v>
+        <v>142</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>55.53775567986045</v>
+        <v>48.54244158966806</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>17.9383876361415</v>
+        <v>22.13916893059711</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.776806020075897</v>
+        <v>0.5780713410641339</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>26.79131172666612</v>
+        <v>-0.6126071199251202</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6613</v>
+        <v>6579</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>278.7082956743713</v>
+        <v>297.1238093422038</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>267</v>
+        <v>164.5</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>39.02089114142221</v>
+        <v>49.98277258133356</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>17.92466641318843</v>
+        <v>14.21627861852767</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.295821904755391</v>
+        <v>1.464210850067146</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-2.564751388353312</v>
+        <v>0.4912583213197818</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6546</v>
+        <v>6835</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>276.6720293204235</v>
+        <v>291.7637366865634</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>61.1</v>
+        <v>31</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>48.6918563128969</v>
+        <v>38.74277447112021</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>34.25128176075999</v>
+        <v>40.4866736066228</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.4540382745166306</v>
+        <v>0.5747743482189597</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.8710308901620962</v>
+        <v>0.1700125172537807</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6741</v>
+        <v>6725</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>257.8532216262795</v>
+        <v>291.6591235557641</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>56</v>
+        <v>247.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>44.16510419880507</v>
+        <v>36.95481889378157</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>28.2945105819129</v>
+        <v>22.19511074119149</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.341542352475842</v>
+        <v>0.6034485681140004</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.2703920026344735</v>
+        <v>-2.024272536679021</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6735</v>
+        <v>6722</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>255.0384157920361</v>
+        <v>290.4601890576815</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>33.25</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>40.91147710545035</v>
+        <v>41.43794222196013</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>29.08415966131303</v>
+        <v>45.09035858844592</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.336062356434631</v>
+        <v>0.6582239260824728</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>1.377746177082622</v>
+        <v>0.0453051647860042</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6568</v>
+        <v>6655</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>253.4327049767064</v>
+        <v>287.1063888918754</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>139.5</v>
+        <v>117.5</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>44.11459787240925</v>
+        <v>48.39343386150986</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>50.3952196306465</v>
+        <v>5.682956899158487</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.5120552148809838</v>
+        <v>0.3740984386145676</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>2.265521062470729</v>
+        <v>0.014379698632841</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6667</v>
+        <v>6683</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>252.4384138177306</v>
+        <v>286.538427429983</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>235.5</v>
+        <v>1230</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>45.71064707908463</v>
+        <v>48.2745948886829</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>26.92820647933205</v>
+        <v>28.25725879420688</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.8239079445400816</v>
+        <v>0.4899732956481283</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>1.098253347595543</v>
+        <v>31.4348537002561</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6581</v>
+        <v>6531</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>248.2253586697184</v>
+        <v>284.7992152405097</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>108</v>
+        <v>923</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>49.67379398493452</v>
+        <v>55.53775567986045</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>13.01856406597112</v>
+        <v>17.9383876361415</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.3520176135133184</v>
+        <v>1.776806020075897</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0219361556607685</v>
+        <v>26.79131172666612</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6515</v>
+        <v>6613</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>241.0314674116884</v>
+        <v>278.7082956743713</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>6830</v>
+        <v>267</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>48.71305714719616</v>
+        <v>39.02089114142221</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>19.23198677474299</v>
+        <v>17.92466641318843</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.9790195446006202</v>
+        <v>1.295821904755391</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>181.6138323572908</v>
+        <v>-2.564751388353312</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6803</v>
+        <v>6546</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>238.6034071093427</v>
+        <v>276.6720293204235</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>271.5</v>
+        <v>61.1</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>43.62915178490819</v>
+        <v>48.6918563128969</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>36.92136146419063</v>
+        <v>34.25128176075999</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.970904696175992</v>
+        <v>0.4540382745166306</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.5411314164166452</v>
+        <v>0.8710308901620962</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6698</v>
+        <v>6741</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>235.1009942776442</v>
+        <v>257.8532216262795</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>34.05</v>
+        <v>56</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>44.76379528547555</v>
+        <v>44.16510419880507</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>23.3107845556375</v>
+        <v>28.2945105819129</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.5893334830166511</v>
+        <v>1.341542352475842</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.2970275502286945</v>
+        <v>0.2703920026344735</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6488</v>
+        <v>6735</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>226.296324417609</v>
+        <v>255.0384157920361</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>854</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,49 +5163,49 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>40.00740011950307</v>
+        <v>40.91147710545035</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>19.6361494784886</v>
+        <v>29.08415966131303</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.6090360424699359</v>
+        <v>1.336062356434631</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-27.16885309080623</v>
+        <v>1.377746177082622</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6654</v>
+        <v>6568</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>224.6346304023602</v>
+        <v>253.4327049767064</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>175.5</v>
+        <v>139.5</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>52.30623216854402</v>
+        <v>44.11459787240925</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>20.35072611833792</v>
+        <v>50.3952196306465</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.5443752742378344</v>
+        <v>0.5120552148809838</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.8049146976001036</v>
+        <v>2.265521062470729</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6695</v>
+        <v>6667</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>223.9700088630154</v>
+        <v>252.4384138177306</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>49.05</v>
+        <v>235.5</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>42.38783163284979</v>
+        <v>45.71064707908463</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>16.84054063700665</v>
+        <v>26.92820647933205</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5859369776776999</v>
+        <v>0.8239079445400816</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.04727762318667</v>
+        <v>1.098253347595543</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6823</v>
+        <v>6581</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>222.3170877585412</v>
+        <v>248.2253586697184</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>64.90000000000001</v>
+        <v>108</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>48.09788649260577</v>
+        <v>49.67379398493452</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>11.80738444797733</v>
+        <v>13.01856406597112</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.8317766514749244</v>
+        <v>0.3520176135133184</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.5813705906331375</v>
+        <v>0.0219361556607685</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6597</v>
+        <v>6515</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>215.8405061488688</v>
+        <v>241.0314674116884</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>67.8</v>
+        <v>6830</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>52.56550927441516</v>
+        <v>48.71305714719616</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>9.227910220942441</v>
+        <v>19.23198677474299</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>2.222963075213416</v>
+        <v>0.9790195446006202</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>1.657113472402883</v>
+        <v>181.6138323572908</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6645</v>
+        <v>6803</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>215.1127092286683</v>
+        <v>238.6034071093427</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>13.3</v>
+        <v>271.5</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>42.2884600426394</v>
+        <v>43.62915178490819</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>23.48003296529696</v>
+        <v>36.92136146419063</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.2648340152809227</v>
+        <v>0.970904696175992</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.0070743341418275</v>
+        <v>0.5411314164166452</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5456,21 +5456,21 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6732</v>
+        <v>6754</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>匯僑設計</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>214.5664754355426</v>
+        <v>236.5725163377126</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>155.5</v>
+        <v>42.6</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>40.31730239668176</v>
+        <v>48.87678235132698</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>21.10849629340524</v>
+        <v>10.07517467247417</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.3001612682267133</v>
+        <v>1.376096931371157</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-1.886577687072621</v>
+        <v>0.1297576362256596</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6674</v>
+        <v>6698</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>211.4543449681333</v>
+        <v>235.1009942776442</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>15.15</v>
+        <v>34.05</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>33.09777697734876</v>
+        <v>44.76379528547555</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>27.94371380273006</v>
+        <v>23.3107845556375</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.233427896138704</v>
+        <v>0.5893334830166511</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.0109324870091924</v>
+        <v>0.2970275502286945</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6485</v>
+        <v>6671</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>三能-KY</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>210.1515967327581</v>
+        <v>226.7570715508206</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>65.2</v>
+        <v>22.65</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>46.58153637139367</v>
+        <v>34.38952071527615</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>31.92566440614958</v>
+        <v>28.84104378582242</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.8886209377032902</v>
+        <v>0.0459561753895343</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>1</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>1.451334781405931</v>
+        <v>0.0708629397155489</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6560</v>
+        <v>6488</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>208.2895459900261</v>
+        <v>226.296324417609</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>32.75</v>
+        <v>854</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,49 +5640,49 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>42.6656646377571</v>
+        <v>40.00740011950307</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>23.55610304861302</v>
+        <v>19.6361494784886</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.09574777521272169</v>
+        <v>0.6090360424699359</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M98" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.2164267139628419</v>
+        <v>-27.16885309080623</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6486</v>
+        <v>6654</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>205.11694768226</v>
+        <v>224.6346304023602</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>74.8</v>
+        <v>175.5</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>37.32295600264841</v>
+        <v>52.30623216854402</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>20.93066759831938</v>
+        <v>20.35072611833792</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.4384345853634585</v>
+        <v>0.5443752742378344</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.0291627746541869</v>
+        <v>0.8049146976001036</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6776</v>
+        <v>6695</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>199.3388245766569</v>
+        <v>223.9700088630154</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>54</v>
+        <v>49.05</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>47.18497562275842</v>
+        <v>42.38783163284979</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>21.12908600125668</v>
+        <v>16.84054063700665</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.6309677549372419</v>
+        <v>0.5859369776776999</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.1513933882284058</v>
+        <v>-0.04727762318667</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6706</v>
+        <v>6823</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>195.4078662588853</v>
+        <v>222.3170877585412</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>115</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>47.36422328239001</v>
+        <v>48.09788649260577</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>27.9360274930259</v>
+        <v>11.80738444797733</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.400283400510497</v>
+        <v>0.8317766514749244</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>3.154285057340575</v>
+        <v>0.5813705906331375</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6668</v>
+        <v>6757</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>台灣虎航-創</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>186.9074690674685</v>
+        <v>215.9226137941733</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>35.25</v>
+        <v>55.6</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>47.20786546979786</v>
+        <v>45.34227041948412</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>14.09140970435063</v>
+        <v>13.93707338204398</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.3209328948822644</v>
+        <v>1.260991760351611</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.1986078361931164</v>
+        <v>0.0573074830071438</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6624</v>
+        <v>6597</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>182.9192891707028</v>
+        <v>215.8405061488688</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>43.55</v>
+        <v>67.8</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>54.1956178298716</v>
+        <v>52.56550927441516</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>10.31840855293046</v>
+        <v>9.227910220942441</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.0808055944507439</v>
+        <v>2.222963075213416</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>3.456389985290163</v>
+        <v>1.657113472402883</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6792</v>
+        <v>6645</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>181.4577717824017</v>
+        <v>215.1127092286683</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>58.1</v>
+        <v>13.3</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>53.53094301456269</v>
+        <v>42.2884600426394</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>20.83237706136118</v>
+        <v>23.48003296529696</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.1071657777679421</v>
+        <v>0.2648340152809227</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.9151082857450872</v>
+        <v>-0.0070743341418275</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, cci_momentum</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6552</v>
+        <v>6732</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>易華電</t>
+          <t>昇佳電子</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>168.5981297540415</v>
+        <v>214.5664754355426</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>24.9</v>
+        <v>155.5</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>42.38434697611292</v>
+        <v>40.31730239668176</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>22.7585018338222</v>
+        <v>21.10849629340524</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.259430816537764</v>
+        <v>0.3001612682267133</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.191439221867006</v>
+        <v>-1.886577687072621</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6498</v>
+        <v>6674</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>久禾光</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>166.1113844479647</v>
+        <v>211.4543449681333</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>77</v>
+        <v>15.15</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>43.16491929246962</v>
+        <v>33.09777697734876</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>38.13070991314</v>
+        <v>27.94371380273006</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.8679145084146477</v>
+        <v>1.233427896138704</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.8198042544683419</v>
+        <v>-0.0109324870091924</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6573</v>
+        <v>6485</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>虹揚-KY</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>163.1716928791651</v>
+        <v>210.1515967327581</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>16.95</v>
+        <v>65.2</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>42.60033215073253</v>
+        <v>46.58153637139367</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>16.91018142212874</v>
+        <v>31.92566440614958</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.5594342595761482</v>
+        <v>0.8886209377032902</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.2575969118523213</v>
+        <v>1.451334781405931</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6643</v>
+        <v>6560</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>M31</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>158.3184728606389</v>
+        <v>208.2895459900261</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>441</v>
+        <v>32.75</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>51.4404446531714</v>
+        <v>42.6656646377571</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>16.8644077092416</v>
+        <v>23.55610304861302</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.6067073503653335</v>
+        <v>0.09574777521272169</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>7.946861437298072</v>
+        <v>0.2164267139628419</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6771</v>
+        <v>6486</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>平和環保-創</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>142.8745263239954</v>
+        <v>205.11694768226</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>38</v>
+        <v>74.8</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>39.90102792412294</v>
+        <v>37.32295600264841</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>13.84143715119434</v>
+        <v>20.93066759831938</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.307740811853606</v>
+        <v>0.4384345853634585</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.07260361763226519</v>
+        <v>-0.0291627746541869</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6558</v>
+        <v>6776</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>興能高</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>132.9799379394085</v>
+        <v>199.3388245766569</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>26.75</v>
+        <v>54</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>49.35985312135943</v>
+        <v>47.18497562275842</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>31.78033287105508</v>
+        <v>21.12908600125668</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.9041300013487308</v>
+        <v>0.6309677549372419</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.2548989916106241</v>
+        <v>0.1513933882284058</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6592</v>
+        <v>6706</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>和潤企業</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>126.7863299962344</v>
+        <v>195.4078662588853</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>60.7</v>
+        <v>115</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>48.91672072180006</v>
+        <v>47.36422328239001</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>12.90889897407236</v>
+        <v>27.9360274930259</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.4326429627152402</v>
+        <v>1.400283400510497</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.09036296809479689</v>
+        <v>3.154285057340575</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6614</v>
+        <v>6668</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>資拓宏宇</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>106.0179244137837</v>
+        <v>186.9074690674685</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>35.85</v>
+        <v>35.25</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>31.111760642823</v>
+        <v>47.20786546979786</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>18.15358759528153</v>
+        <v>14.09140970435063</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.5232085546258598</v>
+        <v>0.3209328948822644</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,62 +6400,804 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.1376631880105543</v>
+        <v>0.1986078361931164</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
+        <v>6624</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>萬年清</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>182.9192891707028</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>43.55</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>54.1956178298716</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>10.31840855293046</v>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>0.0808055944507439</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N113" s="2" t="n">
+        <v>3.456389985290163</v>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>6792</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>詠業</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>181.4577717824017</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>53.53094301456269</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>20.83237706136118</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>0.1071657777679421</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>0.9151082857450872</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, adx_trending, cci_momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>6838</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>台新藥</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>178.997962655958</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>23.35</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>43.64124462171756</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>11.3075077965215</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0.3046090772687889</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>-0.0282389967798287</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>6657</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>華安</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>172.0981768528026</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>38.93922852488689</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>26.98399559157986</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.5488481811716516</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>-0.0388382110682885</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>6552</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>易華電</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>168.5981297540415</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>42.38434697611292</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>22.7585018338222</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0.259430816537764</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>0.191439221867006</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>6498</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>久禾光</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>166.1113844479647</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>43.16491929246962</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>38.13070991314</v>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>0.8679145084146477</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N118" s="2" t="n">
+        <v>0.8198042544683419</v>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>6573</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>虹揚-KY</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>163.1716928791651</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>42.60033215073253</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>16.91018142212874</v>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>0.5594342595761482</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N119" s="2" t="n">
+        <v>-0.2575969118523213</v>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>6643</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>M31</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>158.3184728606389</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>441</v>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>51.4404446531714</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>16.8644077092416</v>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>0.6067073503653335</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N120" s="2" t="n">
+        <v>7.946861437298072</v>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, liquidity_ok, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>6771</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>平和環保-創</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>142.8745263239954</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>39.90102792412294</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>13.84143715119434</v>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>1.307740811853606</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N121" s="2" t="n">
+        <v>0.07260361763226519</v>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>6558</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>興能高</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>132.9799379394085</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>49.35985312135943</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>31.78033287105508</v>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>0.9041300013487308</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N122" s="2" t="n">
+        <v>0.2548989916106241</v>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>6592</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>和潤企業</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>126.7863299962344</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>48.91672072180006</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>12.90889897407236</v>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>0.4326429627152402</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N123" s="2" t="n">
+        <v>0.09036296809479689</v>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>6790</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>永豐實</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>114.9532822370862</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>38.85509119060019</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>17.7362783107566</v>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>0.3760511623577582</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N124" s="2" t="n">
+        <v>-0.0253692892996056</v>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>6614</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>資拓宏宇</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>106.0179244137837</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>35.85</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>31.111760642823</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>18.15358759528153</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>0.5232085546258598</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>-0.1376631880105543</v>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
         <v>6625</v>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>必應</t>
         </is>
       </c>
-      <c r="C113" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D113" s="2" t="n">
+      <c r="C126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="2" t="n">
         <v>91.20556690867112</v>
       </c>
-      <c r="E113" s="2" t="n">
+      <c r="E126" s="2" t="n">
         <v>77.09999999999999</v>
       </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H113" s="2" t="n">
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
         <v>52.7801239412233</v>
       </c>
-      <c r="I113" s="2" t="n">
+      <c r="I126" s="2" t="n">
         <v>16.08133511582697</v>
       </c>
-      <c r="J113" s="2" t="n">
+      <c r="J126" s="2" t="n">
         <v>1.014605467866428</v>
       </c>
-      <c r="K113" s="2" t="n">
+      <c r="K126" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M113" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N113" s="2" t="n">
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="2" t="n">
         <v>0.2843525709206014</v>
       </c>
-      <c r="O113" s="2" t="inlineStr">
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>6794</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>向榮生技-創</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>67.55342853057813</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>38.56417637531845</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>12.83163959576256</v>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>0.8121407443857439</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>-0.195759562686268</v>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>

--- a/output/full_scan/batch_seq7_2026-08-10.xlsx
+++ b/output/full_scan/batch_seq7_2026-08-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6782</v>
+        <v>6589</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>視陽</t>
+          <t>台康生技</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>960.1876249289984</v>
+        <v>903.1291122950096</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>214</v>
+        <v>50.7</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>66.01281568602366</v>
+        <v>63.20820428277012</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>25.55600172008031</v>
+        <v>20.28430258577195</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1.618762492899835</v>
+        <v>2.224597440910823</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>3.678348173758471</v>
+        <v>0.4221706655771498</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6589</v>
+        <v>6606</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>台康生技</t>
+          <t>建德工業</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>903.1291122950096</v>
+        <v>859.2585208683897</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>50.7</v>
+        <v>26.4</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>63.20820428277012</v>
+        <v>64.9322162182639</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>20.28430258577195</v>
+        <v>11.32805055959344</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.224597440910823</v>
+        <v>1.33234245213</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.4221706655771498</v>
+        <v>0.0184664548661789</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6606</v>
+        <v>6716</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>建德工業</t>
+          <t>應廣</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>859.2585208683897</v>
+        <v>808.8507934837611</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>26.4</v>
+        <v>105</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>64.9322162182639</v>
+        <v>66.65619037802345</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>11.32805055959344</v>
+        <v>21.99245011801612</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.33234245213</v>
+        <v>1.408137471200302</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.0184664548661789</v>
+        <v>2.825541977084809</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6716</v>
+        <v>6491</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>應廣</t>
+          <t>晶碩</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>808.8507934837611</v>
+        <v>763.6151179059989</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>105</v>
+        <v>379</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>66.65619037802345</v>
+        <v>65.97135344201988</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>21.99245011801612</v>
+        <v>24.23052685244127</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.408137471200302</v>
+        <v>0.9238484290684073</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>2.825541977084809</v>
+        <v>4.415376844735866</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6491</v>
+        <v>6585</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>晶碩</t>
+          <t>鼎基</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>763.6151179059989</v>
+        <v>759.1229721981631</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>379</v>
+        <v>117.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>65.97135344201988</v>
+        <v>47.42447050181128</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>24.23052685244127</v>
+        <v>19.77777410643681</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.9238484290684073</v>
+        <v>1.738748160150335</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>4.415376844735866</v>
+        <v>-0.1322649076297377</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6585</v>
+        <v>6811</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>鼎基</t>
+          <t>宏碁資訊</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>759.1229721981631</v>
+        <v>748.7586716265645</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>117.5</v>
+        <v>235</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>47.42447050181128</v>
+        <v>54.31271275553281</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>19.77777410643681</v>
+        <v>20.28575397640271</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.738748160150335</v>
+        <v>0.5415195298719717</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.1322649076297377</v>
+        <v>0.4202800286211601</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6811</v>
+        <v>6781</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>宏碁資訊</t>
+          <t>AES-KY</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>748.7586716265645</v>
+        <v>719.8912550996769</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>235</v>
+        <v>1195</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>54.31271275553281</v>
+        <v>63.66996250914878</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>20.28575397640271</v>
+        <v>21.99323176115009</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.5415195298719717</v>
+        <v>2.089125509967689</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.4202800286211601</v>
+        <v>32.35333156805501</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6781</v>
+        <v>6598</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>AES-KY</t>
+          <t>ABC-KY</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>719.8912550996769</v>
+        <v>710.5301595514918</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1195</v>
+        <v>29.4</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>63.66996250914878</v>
+        <v>56.16138578541567</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>21.99323176115009</v>
+        <v>37.81218167631322</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.089125509967689</v>
+        <v>0.3585962222119435</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>32.35333156805501</v>
+        <v>-0.0879665259676758</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6753</v>
+        <v>6532</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>龍德造船</t>
+          <t>瑞耘</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>712.2291274426832</v>
+        <v>697.5891083167379</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>142</v>
+        <v>83.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>54.7974471137344</v>
+        <v>61.98118191778797</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>18.30360133877879</v>
+        <v>30.72823203396104</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.122365272809679</v>
+        <v>2.653578451812226</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.1973597681589906</v>
+        <v>2.656475657580986</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6598</v>
+        <v>6510</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>ABC-KY</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>710.5301595514918</v>
+        <v>683.1425714737663</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>29.4</v>
+        <v>2845</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,49 +1029,49 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>56.16138578541567</v>
+        <v>51.91621449396283</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>37.81218167631322</v>
+        <v>25.15402236835393</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.3585962222119435</v>
+        <v>1.54779792100466</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.0879665259676758</v>
+        <v>58.225230001748</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6532</v>
+        <v>6538</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>瑞耘</t>
+          <t>倉和</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>697.5891083167379</v>
+        <v>679.0725445667794</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>83.5</v>
+        <v>145.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>61.98118191778797</v>
+        <v>55.34335939424123</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>30.72823203396104</v>
+        <v>22.83368063286276</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2.653578451812226</v>
+        <v>0.5449581570377342</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>2.656475657580986</v>
+        <v>0.7470759547209362</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6510</v>
+        <v>6693</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>廣閎科</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>683.1425714737663</v>
+        <v>649.4159036416214</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2845</v>
+        <v>184</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,49 +1135,49 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>51.91621449396283</v>
+        <v>50.38863430194367</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>25.15402236835393</v>
+        <v>26.94908635017923</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.54779792100466</v>
+        <v>3.328927515200341</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>58.225230001748</v>
+        <v>1.716256404857681</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>volume_break, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6538</v>
+        <v>6642</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>倉和</t>
+          <t>富致</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>679.0725445667794</v>
+        <v>628.6846060253871</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>145.5</v>
+        <v>83.3</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>55.34335939424123</v>
+        <v>60.2889815494212</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>22.83368063286276</v>
+        <v>17.20897975546421</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.5449581570377342</v>
+        <v>4.284213476239731</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.7470759547209362</v>
+        <v>1.156990142525024</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6693</v>
+        <v>6761</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>廣閎科</t>
+          <t>穩得</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>649.4159036416214</v>
+        <v>625.7448923331278</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>50.38863430194367</v>
+        <v>54.05048169608121</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>26.94908635017923</v>
+        <v>26.02804642597277</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>3.328927515200341</v>
+        <v>2.362822094468798</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>1.716256404857681</v>
+        <v>3.685602557869743</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6642</v>
+        <v>6530</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>富致</t>
+          <t>創威</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>628.6846060253871</v>
+        <v>612.5901958258647</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>83.3</v>
+        <v>82.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>60.2889815494212</v>
+        <v>55.3255704569258</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>17.20897975546421</v>
+        <v>23.70751846741007</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>4.284213476239731</v>
+        <v>1.819285779096404</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>1</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>1.156990142525024</v>
+        <v>2.232003913636197</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6761</v>
+        <v>6504</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>穩得</t>
+          <t>南六</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>625.7448923331278</v>
+        <v>603.0976881410558</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>168</v>
+        <v>39</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>54.05048169608121</v>
+        <v>56.12879605314978</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>26.02804642597277</v>
+        <v>28.8372696995016</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2.362822094468798</v>
+        <v>0.3446491781906637</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>3.685602557869743</v>
+        <v>-0.0505404410794741</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6530</v>
+        <v>6570</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>創威</t>
+          <t>維田</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>612.5901958258647</v>
+        <v>584.5426196577403</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>82.5</v>
+        <v>57.3</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>55.3255704569258</v>
+        <v>62.78642047667233</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>23.70751846741007</v>
+        <v>17.51839189660703</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.819285779096404</v>
+        <v>2.821798166333596</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>2.232003913636197</v>
+        <v>1.020147977210087</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6504</v>
+        <v>6651</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>南六</t>
+          <t>全宇昕</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>603.0976881410558</v>
+        <v>569.8512544222294</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>39</v>
+        <v>135</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>56.12879605314978</v>
+        <v>55.2073267495169</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>28.8372696995016</v>
+        <v>21.67273944619703</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.3446491781906637</v>
+        <v>2.739427404341888</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.0505404410794741</v>
+        <v>2.065680453017155</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6807</v>
+        <v>6708</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>峰源-KY</t>
+          <t>天擎</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>593.0114392871835</v>
+        <v>567.7426857563656</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>37.9</v>
+        <v>38.8</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>78.94256237876938</v>
+        <v>51.82418142691544</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>16.2922296525899</v>
+        <v>13.21736218561355</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.3965604263811777</v>
+        <v>0.3136627576445495</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.3680542806757046</v>
+        <v>0.6951912532277955</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend, williams_r_recovery, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6570</v>
+        <v>6821</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>維田</t>
+          <t>聯寶</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>584.5426196577403</v>
+        <v>549.7721629012108</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>57.3</v>
+        <v>42.2</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>62.78642047667233</v>
+        <v>39.30309976830468</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>17.51839189660703</v>
+        <v>32.25931406786383</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>2.821798166333596</v>
+        <v>0.4726612092843516</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>1.020147977210087</v>
+        <v>0.7516924578296411</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6651</v>
+        <v>6684</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>全宇昕</t>
+          <t>安格</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>569.8512544222294</v>
+        <v>546.0049317990571</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>135</v>
+        <v>50.2</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>55.2073267495169</v>
+        <v>51.55659956406806</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>21.67273944619703</v>
+        <v>16.81503294795015</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2.739427404341888</v>
+        <v>1.238054269529925</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>2.065680453017155</v>
+        <v>0.1866763663144728</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6708</v>
+        <v>6534</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>天擎</t>
+          <t>正瀚-創</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>567.7426857563656</v>
+        <v>542.5676561431853</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>38.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>51.82418142691544</v>
+        <v>54.26555904583456</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>13.21736218561355</v>
+        <v>23.65710296551155</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.3136627576445495</v>
+        <v>1.529125061183476</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.6951912532277955</v>
+        <v>0.157373213808993</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend, williams_r_recovery, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6666</v>
+        <v>6789</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>羅麗芬-KY</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>560.3756794568671</v>
+        <v>540.558020671125</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>43.25</v>
+        <v>441.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>46.18406819702407</v>
+        <v>45.60821881364068</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>32.47999311729652</v>
+        <v>22.20721067968122</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.4689437146963101</v>
+        <v>0.8306212272732345</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,51 +1736,51 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.298163087406554</v>
+        <v>0.7751631651231854</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6821</v>
+        <v>6806</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>聯寶</t>
+          <t>森崴能源</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>549.7721629012108</v>
+        <v>528.7768356926886</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>42.2</v>
+        <v>3.51</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G25" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>39.30309976830468</v>
+        <v>31.69502831466412</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>32.25931406786383</v>
+        <v>32.5931975692691</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.4726612092843516</v>
+        <v>2.013053626871306</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.7516924578296411</v>
+        <v>0.4112821443334762</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6684</v>
+        <v>6763</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>安格</t>
+          <t>綠界科技</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>546.0049317990571</v>
+        <v>528.6518570733527</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>50.2</v>
+        <v>43.35</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>51.55659956406806</v>
+        <v>50.96655679327223</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>16.81503294795015</v>
+        <v>30.24755573268313</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.238054269529925</v>
+        <v>0.7146723558587027</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.1866763663144728</v>
+        <v>0.3432725437155679</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6534</v>
+        <v>6672</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>正瀚-創</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>542.5676561431853</v>
+        <v>519.6551418881993</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>94.09999999999999</v>
+        <v>251.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>54.26555904583456</v>
+        <v>56.67183179011068</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>23.65710296551155</v>
+        <v>22.66951128365132</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.529125061183476</v>
+        <v>2.069419210418419</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.157373213808993</v>
+        <v>3.476117446306505</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6789</v>
+        <v>6669</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>540.558020671125</v>
+        <v>511.6128318963861</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>441.5</v>
+        <v>6010</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>45.60821881364068</v>
+        <v>60.0720042164613</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>22.20721067968122</v>
+        <v>19.81404541536655</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.8306212272732345</v>
+        <v>0.8392590884643881</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,48 +1948,48 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.7751631651231854</v>
+        <v>78.62252026483554</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6806</v>
+        <v>6640</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>森崴能源</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>528.7768356926886</v>
+        <v>485.7200540579751</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>3.51</v>
+        <v>1005</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G29" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>31.69502831466412</v>
+        <v>54.59927404791888</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>32.5931975692691</v>
+        <v>20.21834003709472</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>2.013053626871306</v>
+        <v>0.2956184699271068</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.4112821443334762</v>
+        <v>20.53216758736876</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6763</v>
+        <v>6584</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>綠界科技</t>
+          <t>南俊國際</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>528.6518570733527</v>
+        <v>469.236949088452</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>43.35</v>
+        <v>522</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>50.96655679327223</v>
+        <v>46.18266784822475</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>30.24755573268313</v>
+        <v>30.31428625478637</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.7146723558587027</v>
+        <v>3.581754449205871</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.3432725437155679</v>
+        <v>7.870487465498378</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6672</v>
+        <v>6742</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>騰輝電子-KY</t>
+          <t>澤米</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>519.6551418881993</v>
+        <v>468.4734612140247</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>251.5</v>
+        <v>44.1</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>56.67183179011068</v>
+        <v>40.82155755577556</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>22.66951128365132</v>
+        <v>21.68416843291506</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>2.069419210418419</v>
+        <v>0.3084014009874118</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>3.476117446306505</v>
+        <v>0.5583314277996085</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6669</v>
+        <v>6805</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>511.6128318963861</v>
+        <v>467.7563613200151</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>6010</v>
+        <v>1755</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>60.0720042164613</v>
+        <v>61.11310339296048</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>19.81404541536655</v>
+        <v>30.83188965682062</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.8392590884643881</v>
+        <v>1.860807352615913</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>78.62252026483554</v>
+        <v>58.4128392384233</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6796</v>
+        <v>6788</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>晉弘</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>494.650318786276</v>
+        <v>463.7194009541718</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>59.8</v>
+        <v>355</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>57.32214159044644</v>
+        <v>47.91640756928628</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>20.11533584545269</v>
+        <v>30.55004940999836</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.97990016579925</v>
+        <v>0.614501683823488</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.2272096422298007</v>
+        <v>5.132820348074866</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, rsi_strong, market_above_ma60, hist_turn_positive, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6640</v>
+        <v>6715</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>均華</t>
+          <t>嘉基</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>485.7200540579751</v>
+        <v>463.4202825676861</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>1005</v>
+        <v>363.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>54.59927404791888</v>
+        <v>47.29255753055375</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>20.21834003709472</v>
+        <v>11.21529419691228</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.2956184699271068</v>
+        <v>0.4688925881836271</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>20.53216758736876</v>
+        <v>1.714932397652252</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6584</v>
+        <v>6829</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>南俊國際</t>
+          <t>千附精密</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>469.236949088452</v>
+        <v>459.3702725398588</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>522</v>
+        <v>200</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>46.18266784822475</v>
+        <v>51.05049877445995</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>30.31428625478637</v>
+        <v>17.61169749460068</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>3.581754449205871</v>
+        <v>0.5689606547922962</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>7.870487465498378</v>
+        <v>1.502692858738342</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6742</v>
+        <v>6830</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>澤米</t>
+          <t>汎銓</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>468.4734612140247</v>
+        <v>453.4382362107434</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>44.1</v>
+        <v>424.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>40.82155755577556</v>
+        <v>52.54861417169353</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>21.68416843291506</v>
+        <v>21.29932834693594</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.3084014009874118</v>
+        <v>1.119607925823429</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.5583314277996085</v>
+        <v>15.16503674177781</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6805</v>
+        <v>6533</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>晶心科</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>467.7563613200151</v>
+        <v>447.4846734611374</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>1755</v>
+        <v>250</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>61.11310339296048</v>
+        <v>63.32615909617144</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>30.83188965682062</v>
+        <v>17.84670684157508</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.860807352615913</v>
+        <v>3.13588276451926</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>58.4128392384233</v>
+        <v>3.770773791979233</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6788</v>
+        <v>6720</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>久昌</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>463.7194009541718</v>
+        <v>438.3484706789851</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>355</v>
+        <v>138.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>47.91640756928628</v>
+        <v>50.82008206964079</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>30.55004940999836</v>
+        <v>29.42633325446777</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.614501683823488</v>
+        <v>0.655303744575668</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>5.132820348074866</v>
+        <v>0.5788071403539399</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6715</v>
+        <v>6743</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>嘉基</t>
+          <t>安普新</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>463.4202825676861</v>
+        <v>437.5575186325199</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>363.5</v>
+        <v>25.95</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>47.29255753055375</v>
+        <v>33.87861410110625</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>11.21529419691228</v>
+        <v>30.65643176615675</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.4688925881836271</v>
+        <v>0.8234789719637171</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>1.714932397652252</v>
+        <v>-0.5587045831037137</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6829</v>
+        <v>6505</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>千附精密</t>
+          <t>台塑化</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>459.3702725398588</v>
+        <v>434.3654160374697</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>200</v>
+        <v>69</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>51.05049877445995</v>
+        <v>49.12673505215231</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>17.61169749460068</v>
+        <v>29.75468960838772</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.5689606547922962</v>
+        <v>0.419620588008366</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>1.502692858738342</v>
+        <v>-1.804791900622028</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6830</v>
+        <v>6561</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>汎銓</t>
+          <t>是方</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>453.4382362107434</v>
+        <v>433.7076490833803</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>424.5</v>
+        <v>327.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>52.54861417169353</v>
+        <v>49.0884234657758</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>21.29932834693594</v>
+        <v>16.62347082415516</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.119607925823429</v>
+        <v>0.5880489855703774</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>15.16503674177781</v>
+        <v>1.208785345212072</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6533</v>
+        <v>6834</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>晶心科</t>
+          <t>天二科技</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>447.4846734611374</v>
+        <v>433.5071841860943</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>250</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>63.32615909617144</v>
+        <v>51.42995958715492</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>17.84670684157508</v>
+        <v>18.11742300721276</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>3.13588276451926</v>
+        <v>1.088022397359117</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>3.770773791979233</v>
+        <v>0.2480144407518252</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6720</v>
+        <v>6680</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>久昌</t>
+          <t>鑫創電子</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>438.3484706789851</v>
+        <v>432.1101223172679</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>138.5</v>
+        <v>52.9</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>50.82008206964079</v>
+        <v>51.35654851602799</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>29.42633325446777</v>
+        <v>8.928063920683451</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.655303744575668</v>
+        <v>0.8490717286048675</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.5788071403539399</v>
+        <v>-1.648866142513686</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, cci_momentum</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6743</v>
+        <v>6739</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>安普新</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>437.5575186325199</v>
+        <v>426.7218206733912</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>25.95</v>
+        <v>1050</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>33.87861410110625</v>
+        <v>49.8735730214248</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>30.65643176615675</v>
+        <v>12.02863743954203</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.8234789719637171</v>
+        <v>0.6696768403733976</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.5587045831037137</v>
+        <v>12.19328639750584</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6505</v>
+        <v>6605</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>台塑化</t>
+          <t>帝寶</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>434.3654160374697</v>
+        <v>423.8067909385865</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>69</v>
+        <v>133.5</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>49.12673505215231</v>
+        <v>48.66613505665759</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>29.75468960838772</v>
+        <v>13.69023809512585</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.419620588008366</v>
+        <v>2.832803818943578</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-1.804791900622028</v>
+        <v>0.7952693072369628</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6561</v>
+        <v>6689</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>是方</t>
+          <t>伊雲谷</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>433.7076490833803</v>
+        <v>423.2327605734614</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>327.5</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>49.0884234657758</v>
+        <v>58.1748589731627</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>16.62347082415516</v>
+        <v>24.78905494688414</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.5880489855703774</v>
+        <v>1.359868348421285</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>1.208785345212072</v>
+        <v>0.6793548770186604</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6834</v>
+        <v>6727</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>天二科技</t>
+          <t>亞泰金屬</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>433.5071841860943</v>
+        <v>416.5573216363507</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>96.59999999999999</v>
+        <v>388</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>51.42995958715492</v>
+        <v>50.23599132197263</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>18.11742300721276</v>
+        <v>15.79112206346012</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.088022397359117</v>
+        <v>1.212936839465476</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.2480144407518252</v>
+        <v>8.790721343260955</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6680</v>
+        <v>6550</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>鑫創電子</t>
+          <t>北極星藥業-KY</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>432.1101223172679</v>
+        <v>410.5408898117086</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>52.9</v>
+        <v>11.25</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>51.35654851602799</v>
+        <v>37.72336004835542</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>8.928063920683451</v>
+        <v>25.85447077230404</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.8490717286048675</v>
+        <v>0.6847241090145594</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>2</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-1.648866142513686</v>
+        <v>0.0228326553656625</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6605</v>
+        <v>6756</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>威鋒電子</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>423.8067909385865</v>
+        <v>407.6224378131971</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>133.5</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>48.66613505665759</v>
+        <v>54.80601789098797</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>13.69023809512585</v>
+        <v>18.41246145425619</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>2.832803818943578</v>
+        <v>0.6046125239328692</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.7952693072369628</v>
+        <v>1.074441310961462</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6689</v>
+        <v>6517</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>伊雲谷</t>
+          <t>保勝光學</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>423.2327605734614</v>
+        <v>402.9592611202101</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>64.09999999999999</v>
+        <v>62</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>58.1748589731627</v>
+        <v>43.65105831595943</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>24.78905494688414</v>
+        <v>17.74264075525872</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.359868348421285</v>
+        <v>0.1284796058816047</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.6793548770186604</v>
+        <v>-0.4950825195650075</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6727</v>
+        <v>6494</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>亞泰金屬</t>
+          <t>九齊</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>416.5573216363507</v>
+        <v>402.5202926201114</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>388</v>
+        <v>55.2</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>50.23599132197263</v>
+        <v>54.1229302849265</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>15.79112206346012</v>
+        <v>27.54430289878499</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.212936839465476</v>
+        <v>1.14580192141777</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>8.790721343260955</v>
+        <v>0.9095012201500574</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6550</v>
+        <v>6658</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>北極星藥業-KY</t>
+          <t>聯策</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>410.5408898117086</v>
+        <v>382.8295496624563</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>11.25</v>
+        <v>161.5</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>37.72336004835542</v>
+        <v>49.57803870758161</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>25.85447077230404</v>
+        <v>23.76831546778813</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.6847241090145594</v>
+        <v>0.7615987252108752</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.0228326553656625</v>
+        <v>2.208044636336305</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6756</v>
+        <v>6691</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>威鋒電子</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>407.6224378131971</v>
+        <v>381.3977196089454</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>99.90000000000001</v>
+        <v>732</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>54.80601789098797</v>
+        <v>56.39326079237441</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>18.41246145425619</v>
+        <v>16.12405063835193</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.6046125239328692</v>
+        <v>0.7817796276097244</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>1.074441310961462</v>
+        <v>6.3943927806036</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6517</v>
+        <v>6541</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>保勝光學</t>
+          <t>泰福-KY</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>402.9592611202101</v>
+        <v>376.8559461019801</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>62</v>
+        <v>38.8</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>43.65105831595943</v>
+        <v>49.35901856634108</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>17.74264075525872</v>
+        <v>9.71640055352052</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.1284796058816047</v>
+        <v>0.634720209292394</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.4950825195650075</v>
+        <v>0.0365724753294625</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6494</v>
+        <v>6679</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>九齊</t>
+          <t>鈺太</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>402.5202926201114</v>
+        <v>369.2154689917006</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>55.2</v>
+        <v>215.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>54.1229302849265</v>
+        <v>43.50356665864479</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>27.54430289878499</v>
+        <v>31.37443742697766</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.14580192141777</v>
+        <v>0.7293921328468287</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.9095012201500574</v>
+        <v>2.322547877028937</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6658</v>
+        <v>6692</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>聯策</t>
+          <t>進能服</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>382.8295496624563</v>
+        <v>359.8501039559089</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>161.5</v>
+        <v>24.25</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>49.57803870758161</v>
+        <v>52.26106510648049</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>23.76831546778813</v>
+        <v>11.43825607522764</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.7615987252108752</v>
+        <v>3.244331776378185</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>2.208044636336305</v>
+        <v>0.5307021697131324</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6691</v>
+        <v>6591</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>動力-KY</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>381.3977196089454</v>
+        <v>357.2464052793781</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>732</v>
+        <v>44.9</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>56.39326079237441</v>
+        <v>42.13820941058614</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>16.12405063835193</v>
+        <v>45.03423550294112</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.7817796276097244</v>
+        <v>1.143389778792955</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>6.3943927806036</v>
+        <v>0.4851264654756431</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6541</v>
+        <v>6664</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>泰福-KY</t>
+          <t>群翊</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>376.8559461019801</v>
+        <v>348.442314200225</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>38.8</v>
+        <v>348</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>49.35901856634108</v>
+        <v>47.45542651341767</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>9.71640055352052</v>
+        <v>25.70798519345708</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.634720209292394</v>
+        <v>0.7454550082529414</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.0365724753294625</v>
+        <v>1.261714691823794</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6679</v>
+        <v>6556</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>鈺太</t>
+          <t>勝品</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>369.2154689917006</v>
+        <v>341</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>215.5</v>
+        <v>61.7</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>43.50356665864479</v>
+        <v>34.5926465168049</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>31.37443742697766</v>
+        <v>24.57604318797957</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.7293921328468287</v>
+        <v>8.973581920851069</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>2.322547877028937</v>
+        <v>0.1846656717517687</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6692</v>
+        <v>6548</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>進能服</t>
+          <t>長科*</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>359.8501039559089</v>
+        <v>336.6128649838843</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>24.25</v>
+        <v>75.7</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>52.26106510648049</v>
+        <v>53.05372729290665</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>11.43825607522764</v>
+        <v>19.98922929557009</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>3.244331776378185</v>
+        <v>0.6025674412759904</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>1</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.5307021697131324</v>
+        <v>1.19829039312493</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6591</v>
+        <v>6799</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>動力-KY</t>
+          <t>來頡</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>357.2464052793781</v>
+        <v>334.0242334417147</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>44.9</v>
+        <v>88</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>42.13820941058614</v>
+        <v>51.70061265124654</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45.03423550294112</v>
+        <v>24.1331473169051</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.143389778792955</v>
+        <v>0.5210397605411677</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.4851264654756431</v>
+        <v>1.525475232754612</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6664</v>
+        <v>6582</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>群翊</t>
+          <t>申豐</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>348.442314200225</v>
+        <v>333.6763982399528</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>348</v>
+        <v>32.1</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>47.45542651341767</v>
+        <v>50.69796412934451</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>25.70798519345708</v>
+        <v>17.04598918768167</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.7454550082529414</v>
+        <v>0.7245360937738936</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>1.261714691823794</v>
+        <v>-0.0357494923945771</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6670</v>
+        <v>6588</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>東典光電</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>343.0914384989764</v>
+        <v>329.377052895135</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>266.5</v>
+        <v>90.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,49 +3785,49 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>53.58976190942653</v>
+        <v>52.17663244556365</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>11.71880494431926</v>
+        <v>19.66415085566471</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.301248206087955</v>
+        <v>0.4659584938125662</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.579237890237448</v>
+        <v>1.975970167190084</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6556</v>
+        <v>6831</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>勝品</t>
+          <t>邁科</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>341</v>
+        <v>327.7859982476213</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>61.7</v>
+        <v>619</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>34.5926465168049</v>
+        <v>47.22838285476606</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>24.57604318797957</v>
+        <v>23.85039667755416</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>8.973581920851069</v>
+        <v>0.92311151391005</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.1846656717517687</v>
+        <v>9.930812126126725</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6548</v>
+        <v>6719</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>長科*</t>
+          <t>力智</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>336.6128649838843</v>
+        <v>325.9158525771313</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>75.7</v>
+        <v>205.5</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>53.05372729290665</v>
+        <v>40.82978142623313</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>19.98922929557009</v>
+        <v>20.79154253108725</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.6025674412759904</v>
+        <v>1.026644398199289</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>1.19829039312493</v>
+        <v>-0.1702043061906515</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6799</v>
+        <v>6577</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>來頡</t>
+          <t>勁豐</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>334.0242334417147</v>
+        <v>323.5857798095538</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>88</v>
+        <v>80.3</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>51.70061265124654</v>
+        <v>51.31890801893034</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>24.1331473169051</v>
+        <v>23.16408226615743</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.5210397605411677</v>
+        <v>0.1266768507117398</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>1.525475232754612</v>
+        <v>-0.3933678215734115</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6582</v>
+        <v>6770</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>申豐</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>333.6763982399528</v>
+        <v>314.947886614597</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>32.1</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>50.69796412934451</v>
+        <v>53.55467541253191</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>17.04598918768167</v>
+        <v>16.20563895511379</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.7245360937738936</v>
+        <v>1.169070819550472</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.0357494923945771</v>
+        <v>1.266537678945586</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6768</v>
+        <v>6526</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>志強-KY</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>332.0837655169215</v>
+        <v>313.9320709299399</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>67.09999999999999</v>
+        <v>627</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>35.49738004222978</v>
+        <v>54.46587496093099</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>34.85998004930307</v>
+        <v>18.71173356855546</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.7981031938357406</v>
+        <v>0.5119133710669493</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.2466406569253871</v>
+        <v>12.25517051224604</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6588</v>
+        <v>6512</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>東典光電</t>
+          <t>啟發電</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>329.377052895135</v>
+        <v>306.7794053218618</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>90.5</v>
+        <v>20.15</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>52.17663244556365</v>
+        <v>52.88827898383956</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>19.66415085566471</v>
+        <v>9.516375216289369</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.4659584938125662</v>
+        <v>1.0453247302729</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>1.975970167190084</v>
+        <v>-0.5929995743408738</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6831</v>
+        <v>6690</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>邁科</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>327.7859982476213</v>
+        <v>305.7510537599638</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>619</v>
+        <v>164</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>47.22838285476606</v>
+        <v>49.94585251032228</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>23.85039667755416</v>
+        <v>20.27595202610962</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.92311151391005</v>
+        <v>0.4089780143845499</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>9.930812126126725</v>
+        <v>0.7435820086444587</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6719</v>
+        <v>6641</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>力智</t>
+          <t>基士德-KY</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>325.9158525771313</v>
+        <v>304.6382874993881</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>205.5</v>
+        <v>18.2</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>40.82978142623313</v>
+        <v>56.43482678571636</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>20.79154253108725</v>
+        <v>12.00180458616351</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.026644398199289</v>
+        <v>0.1768953973291743</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.1702043061906515</v>
+        <v>0.083393593295577</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6577</v>
+        <v>6525</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>勁豐</t>
+          <t>捷敏-KY</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>323.5857798095538</v>
+        <v>302.9680112976309</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>80.3</v>
+        <v>142</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>51.31890801893034</v>
+        <v>48.54244158966806</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>23.16408226615743</v>
+        <v>22.13916893059711</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.1266768507117398</v>
+        <v>0.5780713410641339</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.3933678215734115</v>
+        <v>-0.6126071199251202</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6770</v>
+        <v>6579</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>研揚</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>314.947886614597</v>
+        <v>297.1238093422038</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>67.59999999999999</v>
+        <v>164.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>53.55467541253191</v>
+        <v>49.98277258133356</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>16.20563895511379</v>
+        <v>14.21627861852767</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.169070819550472</v>
+        <v>1.464210850067146</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>1.266537678945586</v>
+        <v>0.4912583213197818</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6526</v>
+        <v>6835</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>圓裕</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>313.9320709299399</v>
+        <v>291.7637366865634</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>627</v>
+        <v>31</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>54.46587496093099</v>
+        <v>38.74277447112021</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>18.71173356855546</v>
+        <v>40.4866736066228</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.5119133710669493</v>
+        <v>0.5747743482189597</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>12.25517051224604</v>
+        <v>0.1700125172537807</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6512</v>
+        <v>6725</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>啟發電</t>
+          <t>矽科宏晟</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>306.7794053218618</v>
+        <v>291.6591235557641</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>20.15</v>
+        <v>247.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>52.88827898383956</v>
+        <v>36.95481889378157</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>9.516375216289369</v>
+        <v>22.19511074119149</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.0453247302729</v>
+        <v>0.6034485681140004</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.5929995743408738</v>
+        <v>-2.024272536679021</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6690</v>
+        <v>6722</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>輝創</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>305.7510537599638</v>
+        <v>290.4601890576815</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>164</v>
+        <v>33.25</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>49.94585251032228</v>
+        <v>41.43794222196013</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>20.27595202610962</v>
+        <v>45.09035858844592</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.4089780143845499</v>
+        <v>0.6582239260824728</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.7435820086444587</v>
+        <v>0.0453051647860042</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6641</v>
+        <v>6655</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>基士德-KY</t>
+          <t>科定</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>304.6382874993881</v>
+        <v>287.1063888918754</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>18.2</v>
+        <v>117.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>56.43482678571636</v>
+        <v>48.39343386150986</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>12.00180458616351</v>
+        <v>5.682956899158487</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.1768953973291743</v>
+        <v>0.3740984386145676</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.083393593295577</v>
+        <v>0.014379698632841</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6525</v>
+        <v>6683</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>捷敏-KY</t>
+          <t>雍智科技</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>302.9680112976309</v>
+        <v>286.538427429983</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>142</v>
+        <v>1230</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>48.54244158966806</v>
+        <v>48.2745948886829</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>22.13916893059711</v>
+        <v>28.25725879420688</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.5780713410641339</v>
+        <v>0.4899732956481283</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.6126071199251202</v>
+        <v>31.4348537002561</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6579</v>
+        <v>6531</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>研揚</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>297.1238093422038</v>
+        <v>284.7992152405097</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>164.5</v>
+        <v>923</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>49.98277258133356</v>
+        <v>55.53775567986045</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>14.21627861852767</v>
+        <v>17.9383876361415</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.464210850067146</v>
+        <v>1.776806020075897</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.4912583213197818</v>
+        <v>26.79131172666612</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6835</v>
+        <v>6613</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>圓裕</t>
+          <t>朋億*</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>291.7637366865634</v>
+        <v>278.7082956743713</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>31</v>
+        <v>267</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>38.74277447112021</v>
+        <v>39.02089114142221</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>40.4866736066228</v>
+        <v>17.92466641318843</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.5747743482189597</v>
+        <v>1.295821904755391</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.1700125172537807</v>
+        <v>-2.564751388353312</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6725</v>
+        <v>6546</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>矽科宏晟</t>
+          <t>正基</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>291.6591235557641</v>
+        <v>276.6720293204235</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>247.5</v>
+        <v>61.1</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>36.95481889378157</v>
+        <v>48.6918563128969</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>22.19511074119149</v>
+        <v>34.25128176075999</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.6034485681140004</v>
+        <v>0.4540382745166306</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>1</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-2.024272536679021</v>
+        <v>0.8710308901620962</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6722</v>
+        <v>6741</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>輝創</t>
+          <t>91APP*-KY</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>290.4601890576815</v>
+        <v>257.8532216262795</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>33.25</v>
+        <v>56</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>41.43794222196013</v>
+        <v>44.16510419880507</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>45.09035858844592</v>
+        <v>28.2945105819129</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.6582239260824728</v>
+        <v>1.341542352475842</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.0453051647860042</v>
+        <v>0.2703920026344735</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6655</v>
+        <v>6735</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>科定</t>
+          <t>美達科技</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>287.1063888918754</v>
+        <v>255.0384157920361</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>117.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>48.39343386150986</v>
+        <v>40.91147710545035</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>5.682956899158487</v>
+        <v>29.08415966131303</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.3740984386145676</v>
+        <v>1.336062356434631</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.014379698632841</v>
+        <v>1.377746177082622</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6683</v>
+        <v>6568</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>雍智科技</t>
+          <t>宏觀</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>286.538427429983</v>
+        <v>253.4327049767064</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>1230</v>
+        <v>139.5</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>48.2745948886829</v>
+        <v>44.11459787240925</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>28.25725879420688</v>
+        <v>50.3952196306465</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.4899732956481283</v>
+        <v>0.5120552148809838</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>31.4348537002561</v>
+        <v>2.265521062470729</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6531</v>
+        <v>6667</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>信紘科</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>284.7992152405097</v>
+        <v>252.4384138177306</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>923</v>
+        <v>235.5</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>55.53775567986045</v>
+        <v>45.71064707908463</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>17.9383876361415</v>
+        <v>26.92820647933205</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.776806020075897</v>
+        <v>0.8239079445400816</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>26.79131172666612</v>
+        <v>1.098253347595543</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6613</v>
+        <v>6581</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>朋億*</t>
+          <t>鋼聯</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>278.7082956743713</v>
+        <v>248.2253586697184</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>267</v>
+        <v>108</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>39.02089114142221</v>
+        <v>49.67379398493452</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>17.92466641318843</v>
+        <v>13.01856406597112</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.295821904755391</v>
+        <v>0.3520176135133184</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-2.564751388353312</v>
+        <v>0.0219361556607685</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6546</v>
+        <v>6515</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>正基</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>276.6720293204235</v>
+        <v>241.0314674116884</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>61.1</v>
+        <v>6830</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>48.6918563128969</v>
+        <v>48.71305714719616</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>34.25128176075999</v>
+        <v>19.23198677474299</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.4540382745166306</v>
+        <v>0.9790195446006202</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.8710308901620962</v>
+        <v>181.6138323572908</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6741</v>
+        <v>6803</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>91APP*-KY</t>
+          <t>崑鼎</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>257.8532216262795</v>
+        <v>238.6034071093427</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>56</v>
+        <v>271.5</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>44.16510419880507</v>
+        <v>43.62915178490819</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>28.2945105819129</v>
+        <v>36.92136146419063</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.341542352475842</v>
+        <v>0.970904696175992</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.2703920026344735</v>
+        <v>0.5411314164166452</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5138,21 +5138,21 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6735</v>
+        <v>6698</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>美達科技</t>
+          <t>旭暉應材</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>255.0384157920361</v>
+        <v>235.1009942776442</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>34.05</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>40.91147710545035</v>
+        <v>44.76379528547555</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>29.08415966131303</v>
+        <v>23.3107845556375</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.336062356434631</v>
+        <v>0.5893334830166511</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>1.377746177082622</v>
+        <v>0.2970275502286945</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6568</v>
+        <v>6488</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>宏觀</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>253.4327049767064</v>
+        <v>226.296324417609</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>139.5</v>
+        <v>854</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,49 +5216,49 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>44.11459787240925</v>
+        <v>40.00740011950307</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>50.3952196306465</v>
+        <v>19.6361494784886</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.5120552148809838</v>
+        <v>0.6090360424699359</v>
       </c>
       <c r="K90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L90" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M90" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>2.265521062470729</v>
+        <v>-27.16885309080623</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6667</v>
+        <v>6654</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>信紘科</t>
+          <t>天正國際</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>252.4384138177306</v>
+        <v>224.6346304023602</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>235.5</v>
+        <v>175.5</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>45.71064707908463</v>
+        <v>52.30623216854402</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>26.92820647933205</v>
+        <v>20.35072611833792</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.8239079445400816</v>
+        <v>0.5443752742378344</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>1.098253347595543</v>
+        <v>0.8049146976001036</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6581</v>
+        <v>6695</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>鋼聯</t>
+          <t>芯鼎</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>248.2253586697184</v>
+        <v>223.9700088630154</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>108</v>
+        <v>49.05</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>49.67379398493452</v>
+        <v>42.38783163284979</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>13.01856406597112</v>
+        <v>16.84054063700665</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.3520176135133184</v>
+        <v>0.5859369776776999</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0219361556607685</v>
+        <v>-0.04727762318667</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6515</v>
+        <v>6823</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>濾能</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>241.0314674116884</v>
+        <v>222.3170877585412</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>6830</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>48.71305714719616</v>
+        <v>48.09788649260577</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>19.23198677474299</v>
+        <v>11.80738444797733</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.9790195446006202</v>
+        <v>0.8317766514749244</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>181.6138323572908</v>
+        <v>0.5813705906331375</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6803</v>
+        <v>6597</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>崑鼎</t>
+          <t>立誠</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>238.6034071093427</v>
+        <v>215.8405061488688</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>271.5</v>
+        <v>67.8</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>43.62915178490819</v>
+        <v>52.56550927441516</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>36.92136146419063</v>
+        <v>9.227910220942441</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.970904696175992</v>
+        <v>2.222963075213416</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.5411314164166452</v>
+        <v>1.657113472402883</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6754</v>
+        <v>6645</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>匯僑設計</t>
+          <t>金萬林-創</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>236.5725163377126</v>
+        <v>215.1127092286683</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>42.6</v>
+        <v>13.3</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>48.87678235132698</v>
+        <v>42.2884600426394</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>10.07517467247417</v>
+        <v>23.48003296529696</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.376096931371157</v>
+        <v>0.2648340152809227</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.1297576362256596</v>
+        <v>-0.0070743341418275</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6698</v>
+        <v>6732</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>旭暉應材</t>
+          <t>昇佳電子</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>235.1009942776442</v>
+        <v>214.5664754355426</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>34.05</v>
+        <v>155.5</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>44.76379528547555</v>
+        <v>40.31730239668176</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>23.3107845556375</v>
+        <v>21.10849629340524</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.5893334830166511</v>
+        <v>0.3001612682267133</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.2970275502286945</v>
+        <v>-1.886577687072621</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6671</v>
+        <v>6674</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>三能-KY</t>
+          <t>鋐寶科技</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>226.7570715508206</v>
+        <v>211.4543449681333</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>22.65</v>
+        <v>15.15</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>34.38952071527615</v>
+        <v>33.09777697734876</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>28.84104378582242</v>
+        <v>27.94371380273006</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.0459561753895343</v>
+        <v>1.233427896138704</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0708629397155489</v>
+        <v>-0.0109324870091924</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6488</v>
+        <v>6485</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>226.296324417609</v>
+        <v>210.1515967327581</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>854</v>
+        <v>65.2</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,49 +5640,49 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>40.00740011950307</v>
+        <v>46.58153637139367</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>19.6361494784886</v>
+        <v>31.92566440614958</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.6090360424699359</v>
+        <v>0.8886209377032902</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-27.16885309080623</v>
+        <v>1.451334781405931</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6654</v>
+        <v>6560</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>天正國際</t>
+          <t>欣普羅</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>224.6346304023602</v>
+        <v>208.2895459900261</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>175.5</v>
+        <v>32.75</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>52.30623216854402</v>
+        <v>42.6656646377571</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>20.35072611833792</v>
+        <v>23.55610304861302</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.5443752742378344</v>
+        <v>0.09574777521272169</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.8049146976001036</v>
+        <v>0.2164267139628419</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6695</v>
+        <v>6486</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>芯鼎</t>
+          <t>互動</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>223.9700088630154</v>
+        <v>205.11694768226</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>49.05</v>
+        <v>74.8</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>42.38783163284979</v>
+        <v>37.32295600264841</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>16.84054063700665</v>
+        <v>20.93066759831938</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.5859369776776999</v>
+        <v>0.4384345853634585</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.04727762318667</v>
+        <v>-0.0291627746541869</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6823</v>
+        <v>6776</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>濾能</t>
+          <t>展碁國際</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>222.3170877585412</v>
+        <v>199.3388245766569</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>64.90000000000001</v>
+        <v>54</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>48.09788649260577</v>
+        <v>47.18497562275842</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>11.80738444797733</v>
+        <v>21.12908600125668</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.8317766514749244</v>
+        <v>0.6309677549372419</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.5813705906331375</v>
+        <v>0.1513933882284058</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6757</v>
+        <v>6706</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>台灣虎航-創</t>
+          <t>惠特</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>215.9226137941733</v>
+        <v>195.4078662588853</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>55.6</v>
+        <v>115</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>45.34227041948412</v>
+        <v>47.36422328239001</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>13.93707338204398</v>
+        <v>27.9360274930259</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.260991760351611</v>
+        <v>1.400283400510497</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.0573074830071438</v>
+        <v>3.154285057340575</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6597</v>
+        <v>6668</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>立誠</t>
+          <t>中揚光</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>215.8405061488688</v>
+        <v>186.9074690674685</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>67.8</v>
+        <v>35.25</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>52.56550927441516</v>
+        <v>47.20786546979786</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>9.227910220942441</v>
+        <v>14.09140970435063</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>2.222963075213416</v>
+        <v>0.3209328948822644</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>1.657113472402883</v>
+        <v>0.1986078361931164</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6645</v>
+        <v>6624</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>金萬林-創</t>
+          <t>萬年清</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>215.1127092286683</v>
+        <v>182.9192891707028</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>13.3</v>
+        <v>43.55</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>42.2884600426394</v>
+        <v>54.1956178298716</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>23.48003296529696</v>
+        <v>10.31840855293046</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.2648340152809227</v>
+        <v>0.0808055944507439</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.0070743341418275</v>
+        <v>3.456389985290163</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6732</v>
+        <v>6792</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>昇佳電子</t>
+          <t>詠業</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>214.5664754355426</v>
+        <v>181.4577717824017</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>155.5</v>
+        <v>58.1</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>40.31730239668176</v>
+        <v>53.53094301456269</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>21.10849629340524</v>
+        <v>20.83237706136118</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.3001612682267133</v>
+        <v>0.1071657777679421</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-1.886577687072621</v>
+        <v>0.9151082857450872</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, adx_trending, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6674</v>
+        <v>6552</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>鋐寶科技</t>
+          <t>易華電</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>211.4543449681333</v>
+        <v>168.5981297540415</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>15.15</v>
+        <v>24.9</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>33.09777697734876</v>
+        <v>42.38434697611292</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>27.94371380273006</v>
+        <v>22.7585018338222</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.233427896138704</v>
+        <v>0.259430816537764</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0109324870091924</v>
+        <v>0.191439221867006</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6092,21 +6092,21 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6485</v>
+        <v>6498</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>久禾光</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>210.1515967327581</v>
+        <v>166.1113844479647</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>65.2</v>
+        <v>77</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>46.58153637139367</v>
+        <v>43.16491929246962</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>31.92566440614958</v>
+        <v>38.13070991314</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.8886209377032902</v>
+        <v>0.8679145084146477</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>1.451334781405931</v>
+        <v>0.8198042544683419</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6560</v>
+        <v>6573</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>欣普羅</t>
+          <t>虹揚-KY</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>208.2895459900261</v>
+        <v>163.1716928791651</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>32.75</v>
+        <v>16.95</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>42.6656646377571</v>
+        <v>42.60033215073253</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>23.55610304861302</v>
+        <v>16.91018142212874</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.09574777521272169</v>
+        <v>0.5594342595761482</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.2164267139628419</v>
+        <v>-0.2575969118523213</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6486</v>
+        <v>6643</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>互動</t>
+          <t>M31</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>205.11694768226</v>
+        <v>158.3184728606389</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>74.8</v>
+        <v>441</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>37.32295600264841</v>
+        <v>51.4404446531714</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>20.93066759831938</v>
+        <v>16.8644077092416</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.4384345853634585</v>
+        <v>0.6067073503653335</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.0291627746541869</v>
+        <v>7.946861437298072</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6776</v>
+        <v>6771</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>展碁國際</t>
+          <t>平和環保-創</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>199.3388245766569</v>
+        <v>142.8745263239954</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>47.18497562275842</v>
+        <v>39.90102792412294</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>21.12908600125668</v>
+        <v>13.84143715119434</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.6309677549372419</v>
+        <v>1.307740811853606</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.1513933882284058</v>
+        <v>0.07260361763226519</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6706</v>
+        <v>6558</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>惠特</t>
+          <t>興能高</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>195.4078662588853</v>
+        <v>132.9799379394085</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>115</v>
+        <v>26.75</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>47.36422328239001</v>
+        <v>49.35985312135943</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>27.9360274930259</v>
+        <v>31.78033287105508</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.400283400510497</v>
+        <v>0.9041300013487308</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>3.154285057340575</v>
+        <v>0.2548989916106241</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6668</v>
+        <v>6592</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>中揚光</t>
+          <t>和潤企業</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>186.9074690674685</v>
+        <v>126.7863299962344</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>35.25</v>
+        <v>60.7</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>47.20786546979786</v>
+        <v>48.91672072180006</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>14.09140970435063</v>
+        <v>12.90889897407236</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.3209328948822644</v>
+        <v>0.4326429627152402</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.1986078361931164</v>
+        <v>0.09036296809479689</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6624</v>
+        <v>6614</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>萬年清</t>
+          <t>資拓宏宇</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>182.9192891707028</v>
+        <v>106.0179244137837</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>43.55</v>
+        <v>35.85</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>54.1956178298716</v>
+        <v>31.111760642823</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>10.31840855293046</v>
+        <v>18.15358759528153</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.0808055944507439</v>
+        <v>0.5232085546258598</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>3.456389985290163</v>
+        <v>-0.1376631880105543</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6792</v>
+        <v>6625</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>詠業</t>
+          <t>必應</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>181.4577717824017</v>
+        <v>91.20556690867112</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>58.1</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>53.53094301456269</v>
+        <v>52.7801239412233</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>20.83237706136118</v>
+        <v>16.08133511582697</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.1071657777679421</v>
+        <v>1.014605467866428</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,698 +6506,9 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.9151082857450872</v>
+        <v>0.2843525709206014</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, adx_trending, cci_momentum</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="n">
-        <v>6838</v>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>台新藥</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D115" s="2" t="n">
-        <v>178.997962655958</v>
-      </c>
-      <c r="E115" s="2" t="n">
-        <v>23.35</v>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H115" s="2" t="n">
-        <v>43.64124462171756</v>
-      </c>
-      <c r="I115" s="2" t="n">
-        <v>11.3075077965215</v>
-      </c>
-      <c r="J115" s="2" t="n">
-        <v>0.3046090772687889</v>
-      </c>
-      <c r="K115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M115" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N115" s="2" t="n">
-        <v>-0.0282389967798287</v>
-      </c>
-      <c r="O115" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="n">
-        <v>6657</v>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>華安</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D116" s="2" t="n">
-        <v>172.0981768528026</v>
-      </c>
-      <c r="E116" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H116" s="2" t="n">
-        <v>38.93922852488689</v>
-      </c>
-      <c r="I116" s="2" t="n">
-        <v>26.98399559157986</v>
-      </c>
-      <c r="J116" s="2" t="n">
-        <v>0.5488481811716516</v>
-      </c>
-      <c r="K116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M116" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N116" s="2" t="n">
-        <v>-0.0388382110682885</v>
-      </c>
-      <c r="O116" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="n">
-        <v>6552</v>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>易華電</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D117" s="2" t="n">
-        <v>168.5981297540415</v>
-      </c>
-      <c r="E117" s="2" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H117" s="2" t="n">
-        <v>42.38434697611292</v>
-      </c>
-      <c r="I117" s="2" t="n">
-        <v>22.7585018338222</v>
-      </c>
-      <c r="J117" s="2" t="n">
-        <v>0.259430816537764</v>
-      </c>
-      <c r="K117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M117" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N117" s="2" t="n">
-        <v>0.191439221867006</v>
-      </c>
-      <c r="O117" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="n">
-        <v>6498</v>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>久禾光</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D118" s="2" t="n">
-        <v>166.1113844479647</v>
-      </c>
-      <c r="E118" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G118" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H118" s="2" t="n">
-        <v>43.16491929246962</v>
-      </c>
-      <c r="I118" s="2" t="n">
-        <v>38.13070991314</v>
-      </c>
-      <c r="J118" s="2" t="n">
-        <v>0.8679145084146477</v>
-      </c>
-      <c r="K118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M118" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N118" s="2" t="n">
-        <v>0.8198042544683419</v>
-      </c>
-      <c r="O118" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="n">
-        <v>6573</v>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>虹揚-KY</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D119" s="2" t="n">
-        <v>163.1716928791651</v>
-      </c>
-      <c r="E119" s="2" t="n">
-        <v>16.95</v>
-      </c>
-      <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G119" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H119" s="2" t="n">
-        <v>42.60033215073253</v>
-      </c>
-      <c r="I119" s="2" t="n">
-        <v>16.91018142212874</v>
-      </c>
-      <c r="J119" s="2" t="n">
-        <v>0.5594342595761482</v>
-      </c>
-      <c r="K119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M119" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N119" s="2" t="n">
-        <v>-0.2575969118523213</v>
-      </c>
-      <c r="O119" s="2" t="inlineStr">
-        <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="n">
-        <v>6643</v>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>M31</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D120" s="2" t="n">
-        <v>158.3184728606389</v>
-      </c>
-      <c r="E120" s="2" t="n">
-        <v>441</v>
-      </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H120" s="2" t="n">
-        <v>51.4404446531714</v>
-      </c>
-      <c r="I120" s="2" t="n">
-        <v>16.8644077092416</v>
-      </c>
-      <c r="J120" s="2" t="n">
-        <v>0.6067073503653335</v>
-      </c>
-      <c r="K120" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L120" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M120" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N120" s="2" t="n">
-        <v>7.946861437298072</v>
-      </c>
-      <c r="O120" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, liquidity_ok, mfi_strong</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="n">
-        <v>6771</v>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>平和環保-創</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D121" s="2" t="n">
-        <v>142.8745263239954</v>
-      </c>
-      <c r="E121" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H121" s="2" t="n">
-        <v>39.90102792412294</v>
-      </c>
-      <c r="I121" s="2" t="n">
-        <v>13.84143715119434</v>
-      </c>
-      <c r="J121" s="2" t="n">
-        <v>1.307740811853606</v>
-      </c>
-      <c r="K121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M121" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N121" s="2" t="n">
-        <v>0.07260361763226519</v>
-      </c>
-      <c r="O121" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="n">
-        <v>6558</v>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>興能高</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D122" s="2" t="n">
-        <v>132.9799379394085</v>
-      </c>
-      <c r="E122" s="2" t="n">
-        <v>26.75</v>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H122" s="2" t="n">
-        <v>49.35985312135943</v>
-      </c>
-      <c r="I122" s="2" t="n">
-        <v>31.78033287105508</v>
-      </c>
-      <c r="J122" s="2" t="n">
-        <v>0.9041300013487308</v>
-      </c>
-      <c r="K122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M122" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N122" s="2" t="n">
-        <v>0.2548989916106241</v>
-      </c>
-      <c r="O122" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, adx_trending</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="n">
-        <v>6592</v>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>和潤企業</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D123" s="2" t="n">
-        <v>126.7863299962344</v>
-      </c>
-      <c r="E123" s="2" t="n">
-        <v>60.7</v>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H123" s="2" t="n">
-        <v>48.91672072180006</v>
-      </c>
-      <c r="I123" s="2" t="n">
-        <v>12.90889897407236</v>
-      </c>
-      <c r="J123" s="2" t="n">
-        <v>0.4326429627152402</v>
-      </c>
-      <c r="K123" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M123" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N123" s="2" t="n">
-        <v>0.09036296809479689</v>
-      </c>
-      <c r="O123" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="n">
-        <v>6790</v>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>永豐實</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D124" s="2" t="n">
-        <v>114.9532822370862</v>
-      </c>
-      <c r="E124" s="2" t="n">
-        <v>38.25</v>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H124" s="2" t="n">
-        <v>38.85509119060019</v>
-      </c>
-      <c r="I124" s="2" t="n">
-        <v>17.7362783107566</v>
-      </c>
-      <c r="J124" s="2" t="n">
-        <v>0.3760511623577582</v>
-      </c>
-      <c r="K124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M124" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N124" s="2" t="n">
-        <v>-0.0253692892996056</v>
-      </c>
-      <c r="O124" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="n">
-        <v>6614</v>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>資拓宏宇</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D125" s="2" t="n">
-        <v>106.0179244137837</v>
-      </c>
-      <c r="E125" s="2" t="n">
-        <v>35.85</v>
-      </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H125" s="2" t="n">
-        <v>31.111760642823</v>
-      </c>
-      <c r="I125" s="2" t="n">
-        <v>18.15358759528153</v>
-      </c>
-      <c r="J125" s="2" t="n">
-        <v>0.5232085546258598</v>
-      </c>
-      <c r="K125" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N125" s="2" t="n">
-        <v>-0.1376631880105543</v>
-      </c>
-      <c r="O125" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="n">
-        <v>6625</v>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>必應</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D126" s="2" t="n">
-        <v>91.20556690867112</v>
-      </c>
-      <c r="E126" s="2" t="n">
-        <v>77.09999999999999</v>
-      </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G126" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H126" s="2" t="n">
-        <v>52.7801239412233</v>
-      </c>
-      <c r="I126" s="2" t="n">
-        <v>16.08133511582697</v>
-      </c>
-      <c r="J126" s="2" t="n">
-        <v>1.014605467866428</v>
-      </c>
-      <c r="K126" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L126" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N126" s="2" t="n">
-        <v>0.2843525709206014</v>
-      </c>
-      <c r="O126" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="n">
-        <v>6794</v>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>向榮生技-創</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D127" s="2" t="n">
-        <v>67.55342853057813</v>
-      </c>
-      <c r="E127" s="2" t="n">
-        <v>74.7</v>
-      </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H127" s="2" t="n">
-        <v>38.56417637531845</v>
-      </c>
-      <c r="I127" s="2" t="n">
-        <v>12.83163959576256</v>
-      </c>
-      <c r="J127" s="2" t="n">
-        <v>0.8121407443857439</v>
-      </c>
-      <c r="K127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N127" s="2" t="n">
-        <v>-0.195759562686268</v>
-      </c>
-      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
